--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
   <si>
     <t>McuSTUDIO_F470VET6</t>
   </si>
@@ -56,6 +56,9 @@
     <t>led_app.o</t>
   </si>
   <si>
+    <t>gd30ad3344.o</t>
+  </si>
+  <si>
     <t>ff.o</t>
   </si>
   <si>
@@ -74,9 +77,6 @@
     <t>oled_app.o</t>
   </si>
   <si>
-    <t>gd30ad3344.o</t>
-  </si>
-  <si>
     <t>adc_app.o</t>
   </si>
   <si>
@@ -101,15 +101,15 @@
     <t>gd32f4xx_sdio.o</t>
   </si>
   <si>
+    <t>gd32f4xx_usart.o</t>
+  </si>
+  <si>
     <t>gd32f4xx_timer.o</t>
   </si>
   <si>
     <t>gd32f4xx_adc.o</t>
   </si>
   <si>
-    <t>gd32f4xx_usart.o</t>
-  </si>
-  <si>
     <t>gd32f4xx_i2c.o</t>
   </si>
   <si>
@@ -140,6 +140,9 @@
     <t>dmul.o</t>
   </si>
   <si>
+    <t>gd32f4xx_dac.o</t>
+  </si>
+  <si>
     <t>ddiv.o</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
     <t>depilogue.o</t>
   </si>
   <si>
-    <t>gd32f4xx_dac.o</t>
-  </si>
-  <si>
     <t>_strtoul.o</t>
   </si>
   <si>
@@ -180,9 +180,6 @@
   </si>
   <si>
     <t>uidiv.o</t>
-  </si>
-  <si>
-    <t>f2d.o</t>
   </si>
   <si>
     <t>strstr.o</t>
@@ -362,9 +359,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$78</c:f>
+              <c:f>ram_percent!$A$3:$A$77</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
                   <c:v>ota_uart.o</c:v>
                 </c:pt>
@@ -402,30 +399,30 @@
                   <c:v>led_app.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>gd30ad3344.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>ff.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>systick.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>oled_app.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>gd30ad3344.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="74">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -433,71 +430,71 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$78</c:f>
+              <c:f>ram_percent!$B$3:$B$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
-                  <c:v>58.73733520507813</c:v>
+                  <c:v>58.72557067871094</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.44456481933594</c:v>
+                  <c:v>23.43986892700195</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.049282073974609</c:v>
+                  <c:v>9.047469139099121</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.854959726333618</c:v>
+                  <c:v>3.862771511077881</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.170969009399414</c:v>
+                  <c:v>3.170333862304688</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.560929536819458</c:v>
+                  <c:v>0.5608171820640564</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5523439049720764</c:v>
+                  <c:v>0.5522332787513733</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1745750159025192</c:v>
+                  <c:v>0.1745400428771973</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1717131286859512</c:v>
+                  <c:v>0.1716787368059158</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1030278727412224</c:v>
+                  <c:v>0.1030072420835495</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.06582336127758026</c:v>
+                  <c:v>0.0658101812005043</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.03434262424707413</c:v>
+                  <c:v>0.03433574736118317</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01717131212353706</c:v>
+                  <c:v>0.01716787368059158</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01144754141569138</c:v>
+                  <c:v>0.01716787368059158</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01144754141569138</c:v>
+                  <c:v>0.01144524849951267</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01144754141569138</c:v>
+                  <c:v>0.01144524849951267</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01144754141569138</c:v>
+                  <c:v>0.01144524849951267</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.005723770707845688</c:v>
+                  <c:v>0.01144524849951267</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.005723770707845688</c:v>
+                  <c:v>0.005722624249756336</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.005723770707845688</c:v>
-                </c:pt>
-                <c:pt idx="75">
+                  <c:v>0.005722624249756336</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -565,20 +562,20 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$78</c:f>
+              <c:f>flash_percent!$A$3:$A$77</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
+                  <c:v>usart_app.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>sdio_sdcard.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>ff.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>oled.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>usart_app.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>mc_w.l</c:v>
@@ -614,25 +611,25 @@
                   <c:v>gd32f4xx_rcu.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>gd30ad3344.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>gd32f4xx_sdio.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
+                  <c:v>gd32f4xx_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>gd32f4xx_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>gd32f4xx_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>gd32f4xx_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>gd30ad3344.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>startup_gd32f450_470.o</c:v>
@@ -674,22 +671,22 @@
                   <c:v>dmul.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>gd32f4xx_dac.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>diskio.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>oled_app.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>scheduler.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>gd32f4xx_dac.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>_strtoul.o</c:v>
@@ -725,75 +722,72 @@
                   <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>f2d.o</c:v>
+                  <c:v>strstr.o</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>strstr.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>memseta.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>memcpya.o</c:v>
+                  <c:v>llsshr.o</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>llsshr.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>init.o</c:v>
+                  <c:v>systick_wrapper_ual.o</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>systick_wrapper_ual.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>llushr.o</c:v>
+                  <c:v>cpp_init.o</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>cpp_init.o</c:v>
+                  <c:v>llshl.o</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>handlers.o</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>_chval.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>memcmp.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>atoi.o</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>strchr.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>gd32f4xx_pmu.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>strlen.o</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>errno.o</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>entry9a.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>entry2.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>entry8a.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>entry5.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
-                  <c:v>llshl.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>handlers.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>_chval.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>memcmp.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>atoi.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>strchr.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>gd32f4xx_pmu.o</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>strlen.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>errno.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>entry9a.o</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>entry2.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>entry8a.o</c:v>
-                </c:pt>
                 <c:pt idx="74">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -801,236 +795,233 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$78</c:f>
+              <c:f>flash_percent!$B$3:$B$77</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="75"/>
                 <c:pt idx="0">
-                  <c:v>13.36861515045166</c:v>
+                  <c:v>12.94747161865234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.04892826080322</c:v>
+                  <c:v>12.42181015014648</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.638339519500732</c:v>
+                  <c:v>10.26641082763672</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.932700634002686</c:v>
+                  <c:v>7.09736967086792</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.904313087463379</c:v>
+                  <c:v>6.513301849365234</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.992193222045898</c:v>
+                  <c:v>4.638631343841553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.781312942504883</c:v>
+                  <c:v>4.442686080932617</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.663706302642822</c:v>
+                  <c:v>4.431381225585938</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.872903823852539</c:v>
+                  <c:v>3.598613262176514</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.497779607772827</c:v>
+                  <c:v>3.250056505203247</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.704949617385864</c:v>
+                  <c:v>2.513376951217651</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.238579034805298</c:v>
+                  <c:v>2.008440732955933</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.727599024772644</c:v>
+                  <c:v>1.605245351791382</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.719488263130188</c:v>
+                  <c:v>1.597708940505981</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.492385983467102</c:v>
+                  <c:v>1.386690735816956</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.297726988792419</c:v>
+                  <c:v>1.382922649383545</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.228785157203674</c:v>
+                  <c:v>1.205818057060242</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.192286610603333</c:v>
+                  <c:v>1.141759037971497</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.086846351623535</c:v>
+                  <c:v>1.107845306396484</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.074680089950562</c:v>
+                  <c:v>1.013640761375427</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.070624709129334</c:v>
+                  <c:v>1.009872674942017</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.009793758392334</c:v>
+                  <c:v>0.9985681176185608</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9408520460128784</c:v>
+                  <c:v>0.8742181062698364</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.888131856918335</c:v>
+                  <c:v>0.8252317309379578</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.8516333103179932</c:v>
+                  <c:v>0.7913181185722351</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.8273009061813355</c:v>
+                  <c:v>0.7687090039253235</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.746192991733551</c:v>
+                  <c:v>0.6933453679084778</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6772512793540955</c:v>
+                  <c:v>0.6292862892150879</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5718109607696533</c:v>
+                  <c:v>0.5313135981559753</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5718109607696533</c:v>
+                  <c:v>0.5313135981559753</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5718109607696533</c:v>
+                  <c:v>0.5313135981559753</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4947583973407745</c:v>
+                  <c:v>0.4597181379795075</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4907030165195465</c:v>
+                  <c:v>0.4559499621391296</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4825921952724457</c:v>
+                  <c:v>0.448413610458374</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4623152315616608</c:v>
+                  <c:v>0.4295727014541626</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4501490294933319</c:v>
+                  <c:v>0.4220363199710846</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.429872065782547</c:v>
+                  <c:v>0.4182681441307068</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.4217612445354462</c:v>
+                  <c:v>0.3994272351264954</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3771519064903259</c:v>
+                  <c:v>0.3918908834457398</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3730964958667755</c:v>
+                  <c:v>0.3504408895969391</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3284871280193329</c:v>
+                  <c:v>0.3466726839542389</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.3203763365745544</c:v>
+                  <c:v>0.2976863384246826</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3163209557533264</c:v>
+                  <c:v>0.2939181625843048</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2879331707954407</c:v>
+                  <c:v>0.2675408720970154</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2859054803848267</c:v>
+                  <c:v>0.2656567990779877</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2271022200584412</c:v>
+                  <c:v>0.2110181599855423</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2068252265453339</c:v>
+                  <c:v>0.1921772509813309</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1987144351005554</c:v>
+                  <c:v>0.1846408993005753</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1987144351005554</c:v>
+                  <c:v>0.1846408993005753</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.0973295196890831</c:v>
+                  <c:v>0.09043635427951813</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.0973295196890831</c:v>
+                  <c:v>0.09043635427951813</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.08921872824430466</c:v>
+                  <c:v>0.08289999514818192</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.07705254107713699</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06782726943492889</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.07299713790416718</c:v>
+                  <c:v>0.06029090285301209</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06488634645938873</c:v>
+                  <c:v>0.06029090285301209</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.06488634645938873</c:v>
+                  <c:v>0.05652272328734398</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.06488634645938873</c:v>
+                  <c:v>0.05652272328734398</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.06083095073699951</c:v>
+                  <c:v>0.05275453999638557</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.06083095073699951</c:v>
+                  <c:v>0.04898636043071747</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.05677555501461029</c:v>
+                  <c:v>0.04898636043071747</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.05272015556693077</c:v>
+                  <c:v>0.03768181428313255</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.05272015556693077</c:v>
+                  <c:v>0.03391363471746445</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.04055396839976311</c:v>
+                  <c:v>0.02637726999819279</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.03649856895208359</c:v>
+                  <c:v>0.02260908856987953</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02838777750730515</c:v>
+                  <c:v>0.01507272571325302</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02433237992227078</c:v>
+                  <c:v>0.01507272571325302</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01622158661484718</c:v>
+                  <c:v>0.007536362856626511</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01622158661484718</c:v>
+                  <c:v>0.007536362856626511</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.008110793307423592</c:v>
+                  <c:v>0.003768181428313255</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.008110793307423592</c:v>
-                </c:pt>
-                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1135,8 +1126,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H77" totalsRowCount="1">
+  <autoFilter ref="A2:H76"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1152,8 +1143,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H77" totalsRowCount="1">
+  <autoFilter ref="A2:H76"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1453,7 +1444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1466,28 +1457,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
         <v>78</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>79</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>83</v>
-      </c>
-      <c r="H2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1495,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>58.73733520507813</v>
+        <v>58.72557067871094</v>
       </c>
       <c r="C3" s="1">
         <v>20524</v>
@@ -1521,7 +1512,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>23.44456481933594</v>
+        <v>23.43986892700195</v>
       </c>
       <c r="C4" s="1">
         <v>8192</v>
@@ -1547,7 +1538,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>9.049282073974609</v>
+        <v>9.047469139099121</v>
       </c>
       <c r="C5" s="1">
         <v>3162</v>
@@ -1573,25 +1564,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>3.854959726333618</v>
+        <v>3.862771511077881</v>
       </c>
       <c r="C6" s="1">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="D6" s="1">
-        <v>3419</v>
+        <v>6872</v>
       </c>
       <c r="E6" s="1">
-        <v>3230</v>
+        <v>6668</v>
       </c>
       <c r="F6" s="1">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="1">
-        <v>1343</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1599,7 +1590,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.170969009399414</v>
+        <v>3.170333862304688</v>
       </c>
       <c r="C7" s="1">
         <v>1108</v>
@@ -1625,7 +1616,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.560929536819458</v>
+        <v>0.5608171820640564</v>
       </c>
       <c r="C8" s="1">
         <v>196</v>
@@ -1651,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5523439049720764</v>
+        <v>0.5522332787513733</v>
       </c>
       <c r="C9" s="1">
         <v>193</v>
@@ -1677,7 +1668,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1745750159025192</v>
+        <v>0.1745400428771973</v>
       </c>
       <c r="C10" s="1">
         <v>61</v>
@@ -1703,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1717131286859512</v>
+        <v>0.1716787368059158</v>
       </c>
       <c r="C11" s="1">
         <v>60</v>
@@ -1729,7 +1720,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1030278727412224</v>
+        <v>0.1030072420835495</v>
       </c>
       <c r="C12" s="1">
         <v>36</v>
@@ -1755,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.06582336127758026</v>
+        <v>0.0658101812005043</v>
       </c>
       <c r="C13" s="1">
         <v>23</v>
@@ -1781,7 +1772,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.03434262424707413</v>
+        <v>0.03433574736118317</v>
       </c>
       <c r="C14" s="1">
         <v>12</v>
@@ -1807,19 +1798,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01717131212353706</v>
+        <v>0.01716787368059158</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
       </c>
       <c r="D15" s="1">
-        <v>5449</v>
+        <v>734</v>
       </c>
       <c r="E15" s="1">
-        <v>5308</v>
+        <v>734</v>
       </c>
       <c r="F15" s="1">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1833,25 +1824,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01144754141569138</v>
+        <v>0.01716787368059158</v>
       </c>
       <c r="C16" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1">
-        <v>3405</v>
+        <v>5449</v>
       </c>
       <c r="E16" s="1">
-        <v>3268</v>
+        <v>5308</v>
       </c>
       <c r="F16" s="1">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G16" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1859,19 +1850,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01144754141569138</v>
+        <v>0.01144524849951267</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>12</v>
+        <v>3457</v>
       </c>
       <c r="E17" s="1">
-        <v>8</v>
+        <v>3320</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -1885,25 +1876,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01144754141569138</v>
+        <v>0.01144524849951267</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1911,25 +1902,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01144754141569138</v>
+        <v>0.01144524849951267</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>588</v>
+        <v>142</v>
       </c>
       <c r="E19" s="1">
-        <v>584</v>
+        <v>142</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>4</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1937,25 +1928,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.005723770707845688</v>
+        <v>0.01144524849951267</v>
       </c>
       <c r="C20" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>208</v>
+        <v>588</v>
       </c>
       <c r="E20" s="1">
-        <v>186</v>
+        <v>584</v>
       </c>
       <c r="F20" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1963,25 +1954,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.005723770707845688</v>
+        <v>0.005722624249756336</v>
       </c>
       <c r="C21" s="1">
         <v>2</v>
       </c>
       <c r="D21" s="1">
-        <v>498</v>
+        <v>208</v>
       </c>
       <c r="E21" s="1">
-        <v>498</v>
+        <v>186</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1989,16 +1980,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.005723770707845688</v>
+        <v>0.005722624249756336</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="1">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2010,35 +2001,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C77">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D77">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E77">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F77">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G77">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H77">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2054,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2067,149 +2058,149 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>83</v>
-      </c>
-      <c r="H2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>13.36861515045166</v>
+        <v>12.94747161865234</v>
       </c>
       <c r="C3" s="1">
-        <v>6593</v>
+        <v>6872</v>
       </c>
       <c r="D3" s="1">
-        <v>61</v>
+        <v>1350</v>
       </c>
       <c r="E3" s="1">
-        <v>6588</v>
+        <v>6668</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="1">
-        <v>56</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>11.04892826080322</v>
+        <v>12.42181015014648</v>
       </c>
       <c r="C4" s="1">
-        <v>5449</v>
+        <v>6593</v>
       </c>
       <c r="D4" s="1">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1">
-        <v>5308</v>
+        <v>6588</v>
       </c>
       <c r="F4" s="1">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" s="1">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>7.638339519500732</v>
+        <v>10.26641082763672</v>
       </c>
       <c r="C5" s="1">
-        <v>3767</v>
+        <v>5449</v>
       </c>
       <c r="D5" s="1">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
-        <v>1672</v>
+        <v>5308</v>
       </c>
       <c r="F5" s="1">
-        <v>2072</v>
+        <v>141</v>
       </c>
       <c r="G5" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>6.932700634002686</v>
+        <v>7.09736967086792</v>
       </c>
       <c r="C6" s="1">
-        <v>3419</v>
+        <v>3767</v>
       </c>
       <c r="D6" s="1">
-        <v>1347</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1">
-        <v>3230</v>
+        <v>1672</v>
       </c>
       <c r="F6" s="1">
-        <v>185</v>
+        <v>2072</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1">
-        <v>1343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>6.904313087463379</v>
+        <v>6.513301849365234</v>
       </c>
       <c r="C7" s="1">
-        <v>3405</v>
+        <v>3457</v>
       </c>
       <c r="D7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>3268</v>
+        <v>3320</v>
       </c>
       <c r="F7" s="1">
         <v>133</v>
@@ -2226,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>4.992193222045898</v>
+        <v>4.638631343841553</v>
       </c>
       <c r="C8" s="1">
         <v>2462</v>
@@ -2252,7 +2243,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="2">
-        <v>4.781312942504883</v>
+        <v>4.442686080932617</v>
       </c>
       <c r="C9" s="1">
         <v>2358</v>
@@ -2278,16 +2269,16 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>4.663706302642822</v>
+        <v>4.431381225585938</v>
       </c>
       <c r="C10" s="1">
-        <v>2300</v>
+        <v>2352</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>2300</v>
+        <v>2352</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -2304,7 +2295,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.872903823852539</v>
+        <v>3.598613262176514</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2330,7 +2321,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>3.497779607772827</v>
+        <v>3.250056505203247</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2356,7 +2347,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>2.704949617385864</v>
+        <v>2.513376951217651</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2382,16 +2373,16 @@
         <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>2.238579034805298</v>
+        <v>2.008440732955933</v>
       </c>
       <c r="C14" s="1">
-        <v>1104</v>
+        <v>1066</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1104</v>
+        <v>1066</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2408,7 +2399,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.727599024772644</v>
+        <v>1.605245351791382</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2434,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.719488263130188</v>
+        <v>1.597708940505981</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2460,7 +2451,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>1.492385983467102</v>
+        <v>1.386690735816956</v>
       </c>
       <c r="C17" s="1">
         <v>736</v>
@@ -2483,19 +2474,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
-        <v>1.297726988792419</v>
+        <v>1.382922649383545</v>
       </c>
       <c r="C18" s="1">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E18" s="1">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2504,24 +2495,24 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
-        <v>1.228785157203674</v>
+        <v>1.205818057060242</v>
       </c>
       <c r="C19" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2535,25 +2526,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>1.192286610603333</v>
+        <v>1.141759037971497</v>
       </c>
       <c r="C20" s="1">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="D20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -2561,25 +2552,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B21" s="2">
-        <v>1.086846351623535</v>
+        <v>1.107845306396484</v>
       </c>
       <c r="C21" s="1">
-        <v>536</v>
+        <v>588</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="1">
-        <v>536</v>
+        <v>584</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -2587,19 +2578,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="2">
-        <v>1.074680089950562</v>
+        <v>1.013640761375427</v>
       </c>
       <c r="C22" s="1">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2613,19 +2604,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>1.070624709129334</v>
+        <v>1.009872674942017</v>
       </c>
       <c r="C23" s="1">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2639,19 +2630,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>1.009793758392334</v>
+        <v>0.9985681176185608</v>
       </c>
       <c r="C24" s="1">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2660,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2668,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9408520460128784</v>
+        <v>0.8742181062698364</v>
       </c>
       <c r="C25" s="1">
         <v>464</v>
@@ -2694,7 +2685,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="2">
-        <v>0.888131856918335</v>
+        <v>0.8252317309379578</v>
       </c>
       <c r="C26" s="1">
         <v>438</v>
@@ -2720,7 +2711,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="2">
-        <v>0.8516333103179932</v>
+        <v>0.7913181185722351</v>
       </c>
       <c r="C27" s="1">
         <v>420</v>
@@ -2746,7 +2737,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="2">
-        <v>0.8273009061813355</v>
+        <v>0.7687090039253235</v>
       </c>
       <c r="C28" s="1">
         <v>408</v>
@@ -2772,7 +2763,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2">
-        <v>0.746192991733551</v>
+        <v>0.6933453679084778</v>
       </c>
       <c r="C29" s="1">
         <v>368</v>
@@ -2798,7 +2789,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6772512793540955</v>
+        <v>0.6292862892150879</v>
       </c>
       <c r="C30" s="1">
         <v>334</v>
@@ -2824,7 +2815,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5718109607696533</v>
+        <v>0.5313135981559753</v>
       </c>
       <c r="C31" s="1">
         <v>282</v>
@@ -2850,7 +2841,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5718109607696533</v>
+        <v>0.5313135981559753</v>
       </c>
       <c r="C32" s="1">
         <v>282</v>
@@ -2876,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5718109607696533</v>
+        <v>0.5313135981559753</v>
       </c>
       <c r="C33" s="1">
         <v>282</v>
@@ -2902,7 +2893,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4947583973407745</v>
+        <v>0.4597181379795075</v>
       </c>
       <c r="C34" s="1">
         <v>244</v>
@@ -2928,7 +2919,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4907030165195465</v>
+        <v>0.4559499621391296</v>
       </c>
       <c r="C35" s="1">
         <v>242</v>
@@ -2954,7 +2945,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4825921952724457</v>
+        <v>0.448413610458374</v>
       </c>
       <c r="C36" s="1">
         <v>238</v>
@@ -2980,7 +2971,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4623152315616608</v>
+        <v>0.4295727014541626</v>
       </c>
       <c r="C37" s="1">
         <v>228</v>
@@ -3006,16 +2997,16 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4501490294933319</v>
+        <v>0.4220363199710846</v>
       </c>
       <c r="C38" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -3032,16 +3023,16 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.429872065782547</v>
+        <v>0.4182681441307068</v>
       </c>
       <c r="C39" s="1">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -3055,71 +3046,71 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.4217612445354462</v>
+        <v>0.3994272351264954</v>
       </c>
       <c r="C40" s="1">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="F40" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3771519064903259</v>
+        <v>0.3918908834457398</v>
       </c>
       <c r="C41" s="1">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="1">
         <v>186</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3730964958667755</v>
+        <v>0.3504408895969391</v>
       </c>
       <c r="C42" s="1">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D42" s="1">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3128,24 +3119,24 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3284871280193329</v>
+        <v>0.3466726839542389</v>
       </c>
       <c r="C43" s="1">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="E43" s="1">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3154,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3162,7 +3153,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.3203763365745544</v>
+        <v>0.2976863384246826</v>
       </c>
       <c r="C44" s="1">
         <v>158</v>
@@ -3188,7 +3179,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3163209557533264</v>
+        <v>0.2939181625843048</v>
       </c>
       <c r="C45" s="1">
         <v>156</v>
@@ -3211,10 +3202,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2879331707954407</v>
+        <v>0.2675408720970154</v>
       </c>
       <c r="C46" s="1">
         <v>142</v>
@@ -3240,7 +3231,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2859054803848267</v>
+        <v>0.2656567990779877</v>
       </c>
       <c r="C47" s="1">
         <v>141</v>
@@ -3266,7 +3257,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2271022200584412</v>
+        <v>0.2110181599855423</v>
       </c>
       <c r="C48" s="1">
         <v>112</v>
@@ -3292,7 +3283,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2068252265453339</v>
+        <v>0.1921772509813309</v>
       </c>
       <c r="C49" s="1">
         <v>102</v>
@@ -3318,7 +3309,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1987144351005554</v>
+        <v>0.1846408993005753</v>
       </c>
       <c r="C50" s="1">
         <v>98</v>
@@ -3344,7 +3335,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1987144351005554</v>
+        <v>0.1846408993005753</v>
       </c>
       <c r="C51" s="1">
         <v>98</v>
@@ -3370,7 +3361,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.0973295196890831</v>
+        <v>0.09043635427951813</v>
       </c>
       <c r="C52" s="1">
         <v>48</v>
@@ -3396,7 +3387,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.0973295196890831</v>
+        <v>0.09043635427951813</v>
       </c>
       <c r="C53" s="1">
         <v>48</v>
@@ -3422,7 +3413,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.08921872824430466</v>
+        <v>0.08289999514818192</v>
       </c>
       <c r="C54" s="1">
         <v>44</v>
@@ -3448,16 +3439,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.07705254107713699</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C55" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3474,7 +3465,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C56" s="1">
         <v>36</v>
@@ -3500,7 +3491,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C57" s="1">
         <v>36</v>
@@ -3526,7 +3517,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3552,7 +3543,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3578,7 +3569,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06782726943492889</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3604,16 +3595,16 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.07299713790416718</v>
+        <v>0.06029090285301209</v>
       </c>
       <c r="C61" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3630,7 +3621,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.06488634645938873</v>
+        <v>0.06029090285301209</v>
       </c>
       <c r="C62" s="1">
         <v>32</v>
@@ -3656,16 +3647,16 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.06488634645938873</v>
+        <v>0.05652272328734398</v>
       </c>
       <c r="C63" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3679,19 +3670,19 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.06488634645938873</v>
+        <v>0.05652272328734398</v>
       </c>
       <c r="C64" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3700,24 +3691,24 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.06083095073699951</v>
+        <v>0.05275453999638557</v>
       </c>
       <c r="C65" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3731,19 +3722,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.06083095073699951</v>
+        <v>0.04898636043071747</v>
       </c>
       <c r="C66" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3757,19 +3748,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.05677555501461029</v>
+        <v>0.04898636043071747</v>
       </c>
       <c r="C67" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3783,19 +3774,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.05272015556693077</v>
+        <v>0.03768181428313255</v>
       </c>
       <c r="C68" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3809,19 +3800,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.05272015556693077</v>
+        <v>0.03391363471746445</v>
       </c>
       <c r="C69" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3835,19 +3826,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.04055396839976311</v>
+        <v>0.02637726999819279</v>
       </c>
       <c r="C70" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3861,25 +3852,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="B71" s="2">
-        <v>0.03649856895208359</v>
+        <v>0.02260908856987953</v>
       </c>
       <c r="C71" s="1">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -3890,16 +3881,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02838777750730515</v>
+        <v>0.01507272571325302</v>
       </c>
       <c r="C72" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -3913,16 +3904,16 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02433237992227078</v>
+        <v>0.01507272571325302</v>
       </c>
       <c r="C73" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
         <v>8</v>
@@ -3931,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3939,19 +3930,19 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01622158661484718</v>
+        <v>0.007536362856626511</v>
       </c>
       <c r="C74" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3965,19 +3956,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01622158661484718</v>
+        <v>0.007536362856626511</v>
       </c>
       <c r="C75" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3991,19 +3982,19 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B76" s="2">
-        <v>0.008110793307423592</v>
+        <v>0.003768181428313255</v>
       </c>
       <c r="C76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4012,64 +4003,38 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="2">
-        <v>0.008110793307423592</v>
-      </c>
-      <c r="C77" s="1">
-        <v>4</v>
-      </c>
-      <c r="D77" s="1">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1">
-        <v>4</v>
-      </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C77">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D77">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E77">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F77">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G77">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H77">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
   <si>
     <t>McuSTUDIO_F470VET6</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>uidiv.o</t>
+  </si>
+  <si>
+    <t>f2d.o</t>
   </si>
   <si>
     <t>strstr.o</t>
@@ -359,9 +362,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$77</c:f>
+              <c:f>ram_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>ota_uart.o</c:v>
                 </c:pt>
@@ -422,7 +425,7 @@
                 <c:pt idx="19">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -430,10 +433,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$77</c:f>
+              <c:f>ram_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>58.72557067871094</c:v>
                 </c:pt>
@@ -494,7 +497,7 @@
                 <c:pt idx="19">
                   <c:v>0.005722624249756336</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -562,9 +565,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$77</c:f>
+              <c:f>flash_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
                   <c:v>usart_app.o</c:v>
                 </c:pt>
@@ -722,72 +725,75 @@
                   <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="52">
+                  <c:v>f2d.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
                   <c:v>strstr.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>systick_wrapper_ual.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>_chval.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>atoi.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>gd32f4xx_pmu.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>entry8a.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -795,233 +801,236 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$77</c:f>
+              <c:f>flash_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="75"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>12.94747161865234</c:v>
+                  <c:v>14.05118274688721</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.42181015014648</c:v>
+                  <c:v>12.24417781829834</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.26641082763672</c:v>
+                  <c:v>10.11960029602051</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.09736967086792</c:v>
+                  <c:v>6.995877265930176</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.513301849365234</c:v>
+                  <c:v>6.420161247253418</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.638631343841553</c:v>
+                  <c:v>4.572299003601074</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.442686080932617</c:v>
+                  <c:v>4.379155158996582</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.431381225585938</c:v>
+                  <c:v>4.368012428283691</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.598613262176514</c:v>
+                  <c:v>3.547152996063232</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.250056505203247</c:v>
+                  <c:v>3.203580617904663</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.513376951217651</c:v>
+                  <c:v>2.47743558883667</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.008440732955933</c:v>
+                  <c:v>2.050291538238525</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.605245351791382</c:v>
+                  <c:v>1.582290291786194</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.597708940505981</c:v>
+                  <c:v>1.574861645698547</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.386690735816956</c:v>
+                  <c:v>1.36686110496521</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.382922649383545</c:v>
+                  <c:v>1.363146781921387</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.205818057060242</c:v>
+                  <c:v>1.18857479095459</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.141759037971497</c:v>
+                  <c:v>1.125431776046753</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.107845306396484</c:v>
+                  <c:v>1.092003107070923</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.013640761375427</c:v>
+                  <c:v>0.9991456866264343</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.009872674942017</c:v>
+                  <c:v>0.9954314231872559</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9985681176185608</c:v>
+                  <c:v>0.9842885136604309</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8742181062698364</c:v>
+                  <c:v>0.8617167472839356</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8252317309379578</c:v>
+                  <c:v>0.8134309053421021</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.7913181185722351</c:v>
+                  <c:v>0.780002236366272</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7687090039253235</c:v>
+                  <c:v>0.7577164769172669</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6933453679084778</c:v>
+                  <c:v>0.683430552482605</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6292862892150879</c:v>
+                  <c:v>0.6202874779701233</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5313135981559753</c:v>
+                  <c:v>0.5237157940864563</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5313135981559753</c:v>
+                  <c:v>0.5237157940864563</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5313135981559753</c:v>
+                  <c:v>0.5237157940864563</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4597181379795075</c:v>
+                  <c:v>0.4531441628932953</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4559499621391296</c:v>
+                  <c:v>0.4494298696517944</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.448413610458374</c:v>
+                  <c:v>0.4420012533664703</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4295727014541626</c:v>
+                  <c:v>0.4234297871589661</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4220363199710846</c:v>
+                  <c:v>0.4160012006759644</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4182681441307068</c:v>
+                  <c:v>0.4122868776321411</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3994272351264954</c:v>
+                  <c:v>0.3937154114246368</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3918908834457398</c:v>
+                  <c:v>0.3862868249416351</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3504408895969391</c:v>
+                  <c:v>0.3454295694828033</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3466726839542389</c:v>
+                  <c:v>0.3417152762413025</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2976863384246826</c:v>
+                  <c:v>0.2934294044971466</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2939181625843048</c:v>
+                  <c:v>0.2897151112556458</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2675408720970154</c:v>
+                  <c:v>0.2637150287628174</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2656567990779877</c:v>
+                  <c:v>0.2618578970432282</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2110181599855423</c:v>
+                  <c:v>0.2080006003379822</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1921772509813309</c:v>
+                  <c:v>0.1894291192293167</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1846408993005753</c:v>
+                  <c:v>0.1820005178451538</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1846408993005753</c:v>
+                  <c:v>0.1820005178451538</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.09043635427951813</c:v>
+                  <c:v>0.08914311230182648</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.09043635427951813</c:v>
+                  <c:v>0.08914311230182648</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.08289999514818192</c:v>
+                  <c:v>0.08171451836824417</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.07057163119316101</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.06782726943492889</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.06029090285301209</c:v>
+                  <c:v>0.06685733050107956</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06029090285301209</c:v>
+                  <c:v>0.05942874029278755</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.05652272328734398</c:v>
+                  <c:v>0.05942874029278755</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.05652272328734398</c:v>
+                  <c:v>0.0557144433259964</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.05275453999638557</c:v>
+                  <c:v>0.0557144433259964</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.04898636043071747</c:v>
+                  <c:v>0.05200015008449554</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.04898636043071747</c:v>
+                  <c:v>0.04828585311770439</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.03768181428313255</c:v>
+                  <c:v>0.04828585311770439</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.03391363471746445</c:v>
+                  <c:v>0.03714296221733093</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.02637726999819279</c:v>
+                  <c:v>0.03342866525053978</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02260908856987953</c:v>
+                  <c:v>0.02600007504224777</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.01507272571325302</c:v>
+                  <c:v>0.02228577807545662</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.01507272571325302</c:v>
+                  <c:v>0.01485718507319689</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.007536362856626511</c:v>
+                  <c:v>0.01485718507319689</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.007536362856626511</c:v>
+                  <c:v>0.007428592536598444</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.003768181428313255</c:v>
+                  <c:v>0.007428592536598444</c:v>
                 </c:pt>
                 <c:pt idx="74">
+                  <c:v>0.003714296268299222</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1126,8 +1135,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H77" totalsRowCount="1">
-  <autoFilter ref="A2:H76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1143,8 +1152,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H77" totalsRowCount="1">
-  <autoFilter ref="A2:H76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1444,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1457,28 +1466,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1570,10 +1579,10 @@
         <v>1350</v>
       </c>
       <c r="D6" s="1">
-        <v>6872</v>
+        <v>7566</v>
       </c>
       <c r="E6" s="1">
-        <v>6668</v>
+        <v>7362</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>
@@ -2001,35 +2010,35 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-      <c r="B77">
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C77">
+      <c r="C78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D77">
+      <c r="D78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E77">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F77">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G77">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H77">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2045,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2058,28 +2067,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
         <v>84</v>
-      </c>
-      <c r="C2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2087,16 +2096,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>12.94747161865234</v>
+        <v>14.05118274688721</v>
       </c>
       <c r="C3" s="1">
-        <v>6872</v>
+        <v>7566</v>
       </c>
       <c r="D3" s="1">
         <v>1350</v>
       </c>
       <c r="E3" s="1">
-        <v>6668</v>
+        <v>7362</v>
       </c>
       <c r="F3" s="1">
         <v>200</v>
@@ -2113,7 +2122,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>12.42181015014648</v>
+        <v>12.24417781829834</v>
       </c>
       <c r="C4" s="1">
         <v>6593</v>
@@ -2139,7 +2148,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="2">
-        <v>10.26641082763672</v>
+        <v>10.11960029602051</v>
       </c>
       <c r="C5" s="1">
         <v>5449</v>
@@ -2165,7 +2174,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>7.09736967086792</v>
+        <v>6.995877265930176</v>
       </c>
       <c r="C6" s="1">
         <v>3767</v>
@@ -2191,7 +2200,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="2">
-        <v>6.513301849365234</v>
+        <v>6.420161247253418</v>
       </c>
       <c r="C7" s="1">
         <v>3457</v>
@@ -2217,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>4.638631343841553</v>
+        <v>4.572299003601074</v>
       </c>
       <c r="C8" s="1">
         <v>2462</v>
@@ -2243,7 +2252,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="2">
-        <v>4.442686080932617</v>
+        <v>4.379155158996582</v>
       </c>
       <c r="C9" s="1">
         <v>2358</v>
@@ -2269,7 +2278,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="2">
-        <v>4.431381225585938</v>
+        <v>4.368012428283691</v>
       </c>
       <c r="C10" s="1">
         <v>2352</v>
@@ -2295,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.598613262176514</v>
+        <v>3.547152996063232</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2321,7 +2330,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="2">
-        <v>3.250056505203247</v>
+        <v>3.203580617904663</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2347,7 +2356,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2">
-        <v>2.513376951217651</v>
+        <v>2.47743558883667</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2373,16 +2382,16 @@
         <v>24</v>
       </c>
       <c r="B14" s="2">
-        <v>2.008440732955933</v>
+        <v>2.050291538238525</v>
       </c>
       <c r="C14" s="1">
-        <v>1066</v>
+        <v>1104</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1066</v>
+        <v>1104</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2399,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.605245351791382</v>
+        <v>1.582290291786194</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2425,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.597708940505981</v>
+        <v>1.574861645698547</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2451,7 +2460,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2">
-        <v>1.386690735816956</v>
+        <v>1.36686110496521</v>
       </c>
       <c r="C17" s="1">
         <v>736</v>
@@ -2477,7 +2486,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2">
-        <v>1.382922649383545</v>
+        <v>1.363146781921387</v>
       </c>
       <c r="C18" s="1">
         <v>734</v>
@@ -2503,7 +2512,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="2">
-        <v>1.205818057060242</v>
+        <v>1.18857479095459</v>
       </c>
       <c r="C19" s="1">
         <v>640</v>
@@ -2529,7 +2538,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>1.141759037971497</v>
+        <v>1.125431776046753</v>
       </c>
       <c r="C20" s="1">
         <v>606</v>
@@ -2555,7 +2564,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2">
-        <v>1.107845306396484</v>
+        <v>1.092003107070923</v>
       </c>
       <c r="C21" s="1">
         <v>588</v>
@@ -2581,7 +2590,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="2">
-        <v>1.013640761375427</v>
+        <v>0.9991456866264343</v>
       </c>
       <c r="C22" s="1">
         <v>538</v>
@@ -2607,7 +2616,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2">
-        <v>1.009872674942017</v>
+        <v>0.9954314231872559</v>
       </c>
       <c r="C23" s="1">
         <v>536</v>
@@ -2633,7 +2642,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="2">
-        <v>0.9985681176185608</v>
+        <v>0.9842885136604309</v>
       </c>
       <c r="C24" s="1">
         <v>530</v>
@@ -2659,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8742181062698364</v>
+        <v>0.8617167472839356</v>
       </c>
       <c r="C25" s="1">
         <v>464</v>
@@ -2685,7 +2694,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8252317309379578</v>
+        <v>0.8134309053421021</v>
       </c>
       <c r="C26" s="1">
         <v>438</v>
@@ -2711,7 +2720,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="2">
-        <v>0.7913181185722351</v>
+        <v>0.780002236366272</v>
       </c>
       <c r="C27" s="1">
         <v>420</v>
@@ -2737,7 +2746,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7687090039253235</v>
+        <v>0.7577164769172669</v>
       </c>
       <c r="C28" s="1">
         <v>408</v>
@@ -2763,7 +2772,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6933453679084778</v>
+        <v>0.683430552482605</v>
       </c>
       <c r="C29" s="1">
         <v>368</v>
@@ -2789,7 +2798,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6292862892150879</v>
+        <v>0.6202874779701233</v>
       </c>
       <c r="C30" s="1">
         <v>334</v>
@@ -2815,7 +2824,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5313135981559753</v>
+        <v>0.5237157940864563</v>
       </c>
       <c r="C31" s="1">
         <v>282</v>
@@ -2841,7 +2850,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5313135981559753</v>
+        <v>0.5237157940864563</v>
       </c>
       <c r="C32" s="1">
         <v>282</v>
@@ -2867,7 +2876,7 @@
         <v>6</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5313135981559753</v>
+        <v>0.5237157940864563</v>
       </c>
       <c r="C33" s="1">
         <v>282</v>
@@ -2893,7 +2902,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4597181379795075</v>
+        <v>0.4531441628932953</v>
       </c>
       <c r="C34" s="1">
         <v>244</v>
@@ -2919,7 +2928,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4559499621391296</v>
+        <v>0.4494298696517944</v>
       </c>
       <c r="C35" s="1">
         <v>242</v>
@@ -2945,7 +2954,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>0.448413610458374</v>
+        <v>0.4420012533664703</v>
       </c>
       <c r="C36" s="1">
         <v>238</v>
@@ -2971,7 +2980,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4295727014541626</v>
+        <v>0.4234297871589661</v>
       </c>
       <c r="C37" s="1">
         <v>228</v>
@@ -2997,7 +3006,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4220363199710846</v>
+        <v>0.4160012006759644</v>
       </c>
       <c r="C38" s="1">
         <v>224</v>
@@ -3023,7 +3032,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4182681441307068</v>
+        <v>0.4122868776321411</v>
       </c>
       <c r="C39" s="1">
         <v>222</v>
@@ -3049,7 +3058,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3994272351264954</v>
+        <v>0.3937154114246368</v>
       </c>
       <c r="C40" s="1">
         <v>212</v>
@@ -3075,7 +3084,7 @@
         <v>19</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3918908834457398</v>
+        <v>0.3862868249416351</v>
       </c>
       <c r="C41" s="1">
         <v>208</v>
@@ -3101,7 +3110,7 @@
         <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3504408895969391</v>
+        <v>0.3454295694828033</v>
       </c>
       <c r="C42" s="1">
         <v>186</v>
@@ -3127,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3466726839542389</v>
+        <v>0.3417152762413025</v>
       </c>
       <c r="C43" s="1">
         <v>184</v>
@@ -3153,7 +3162,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2976863384246826</v>
+        <v>0.2934294044971466</v>
       </c>
       <c r="C44" s="1">
         <v>158</v>
@@ -3179,7 +3188,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2939181625843048</v>
+        <v>0.2897151112556458</v>
       </c>
       <c r="C45" s="1">
         <v>156</v>
@@ -3205,7 +3214,7 @@
         <v>17</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2675408720970154</v>
+        <v>0.2637150287628174</v>
       </c>
       <c r="C46" s="1">
         <v>142</v>
@@ -3231,7 +3240,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2656567990779877</v>
+        <v>0.2618578970432282</v>
       </c>
       <c r="C47" s="1">
         <v>141</v>
@@ -3257,7 +3266,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2110181599855423</v>
+        <v>0.2080006003379822</v>
       </c>
       <c r="C48" s="1">
         <v>112</v>
@@ -3283,7 +3292,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.1921772509813309</v>
+        <v>0.1894291192293167</v>
       </c>
       <c r="C49" s="1">
         <v>102</v>
@@ -3309,7 +3318,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1846408993005753</v>
+        <v>0.1820005178451538</v>
       </c>
       <c r="C50" s="1">
         <v>98</v>
@@ -3335,7 +3344,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1846408993005753</v>
+        <v>0.1820005178451538</v>
       </c>
       <c r="C51" s="1">
         <v>98</v>
@@ -3361,7 +3370,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.09043635427951813</v>
+        <v>0.08914311230182648</v>
       </c>
       <c r="C52" s="1">
         <v>48</v>
@@ -3387,7 +3396,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.09043635427951813</v>
+        <v>0.08914311230182648</v>
       </c>
       <c r="C53" s="1">
         <v>48</v>
@@ -3413,7 +3422,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.08289999514818192</v>
+        <v>0.08171451836824417</v>
       </c>
       <c r="C54" s="1">
         <v>44</v>
@@ -3439,16 +3448,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.07057163119316101</v>
       </c>
       <c r="C55" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3465,7 +3474,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C56" s="1">
         <v>36</v>
@@ -3491,7 +3500,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C57" s="1">
         <v>36</v>
@@ -3517,7 +3526,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3543,7 +3552,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3569,7 +3578,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.06782726943492889</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3595,16 +3604,16 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.06029090285301209</v>
+        <v>0.06685733050107956</v>
       </c>
       <c r="C61" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3621,7 +3630,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.06029090285301209</v>
+        <v>0.05942874029278755</v>
       </c>
       <c r="C62" s="1">
         <v>32</v>
@@ -3647,16 +3656,16 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.05652272328734398</v>
+        <v>0.05942874029278755</v>
       </c>
       <c r="C63" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3673,7 +3682,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.05652272328734398</v>
+        <v>0.0557144433259964</v>
       </c>
       <c r="C64" s="1">
         <v>30</v>
@@ -3699,16 +3708,16 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.05275453999638557</v>
+        <v>0.0557144433259964</v>
       </c>
       <c r="C65" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3725,16 +3734,16 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.04898636043071747</v>
+        <v>0.05200015008449554</v>
       </c>
       <c r="C66" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3751,7 +3760,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.04898636043071747</v>
+        <v>0.04828585311770439</v>
       </c>
       <c r="C67" s="1">
         <v>26</v>
@@ -3777,16 +3786,16 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.03768181428313255</v>
+        <v>0.04828585311770439</v>
       </c>
       <c r="C68" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3803,16 +3812,16 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.03391363471746445</v>
+        <v>0.03714296221733093</v>
       </c>
       <c r="C69" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3829,16 +3838,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.02637726999819279</v>
+        <v>0.03342866525053978</v>
       </c>
       <c r="C70" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3852,25 +3861,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02260908856987953</v>
+        <v>0.02600007504224777</v>
       </c>
       <c r="C71" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -3878,16 +3887,16 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="B72" s="2">
-        <v>0.01507272571325302</v>
+        <v>0.02228577807545662</v>
       </c>
       <c r="C72" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
         <v>8</v>
@@ -3896,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -3907,7 +3916,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2">
-        <v>0.01507272571325302</v>
+        <v>0.01485718507319689</v>
       </c>
       <c r="C73" s="1">
         <v>8</v>
@@ -3933,16 +3942,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.007536362856626511</v>
+        <v>0.01485718507319689</v>
       </c>
       <c r="C74" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -3959,7 +3968,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.007536362856626511</v>
+        <v>0.007428592536598444</v>
       </c>
       <c r="C75" s="1">
         <v>4</v>
@@ -3982,59 +3991,85 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.007428592536598444</v>
+      </c>
+      <c r="C76" s="1">
+        <v>4</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="2">
-        <v>0.003768181428313255</v>
-      </c>
-      <c r="C76" s="1">
+      <c r="B77" s="2">
+        <v>0.003714296268299222</v>
+      </c>
+      <c r="C77" s="1">
         <v>2</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D77" s="1">
         <v>2</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="1">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-      <c r="B77">
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C77">
+      <c r="C78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D77">
+      <c r="D78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E77">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F77">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G77">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H77">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="87">
   <si>
     <t>McuSTUDIO_F470VET6</t>
   </si>
@@ -53,6 +53,9 @@
     <t>oled.o</t>
   </si>
   <si>
+    <t>gd32f4xx_pmu.o</t>
+  </si>
+  <si>
     <t>led_app.o</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>gd32f4xx_rtc.o</t>
+  </si>
+  <si>
     <t>gd32f4xx_rcu.o</t>
   </si>
   <si>
@@ -113,9 +119,6 @@
     <t>gd32f4xx_i2c.o</t>
   </si>
   <si>
-    <t>gd32f4xx_rtc.o</t>
-  </si>
-  <si>
     <t>gd32f4xx_fmc.o</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
     <t>dadd.o</t>
   </si>
   <si>
+    <t>gd32f4xx_it.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -134,9 +140,6 @@
     <t>gd32f4xx_misc.o</t>
   </si>
   <si>
-    <t>gd32f4xx_it.o</t>
-  </si>
-  <si>
     <t>dmul.o</t>
   </si>
   <si>
@@ -152,6 +155,9 @@
     <t>depilogue.o</t>
   </si>
   <si>
+    <t>gd32f4xx_exti.o</t>
+  </si>
+  <si>
     <t>_strtoul.o</t>
   </si>
   <si>
@@ -225,9 +231,6 @@
   </si>
   <si>
     <t>strchr.o</t>
-  </si>
-  <si>
-    <t>gd32f4xx_pmu.o</t>
   </si>
   <si>
     <t>strlen.o</t>
@@ -362,9 +365,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$78</c:f>
+              <c:f>ram_percent!$A$3:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>ota_uart.o</c:v>
                 </c:pt>
@@ -399,33 +402,36 @@
                   <c:v>oled.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>gd32f4xx_pmu.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>led_app.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>gd30ad3344.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>ff.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>systick.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>oled_app.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -433,71 +439,74 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$78</c:f>
+              <c:f>ram_percent!$B$3:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>58.72557067871094</c:v>
+                  <c:v>58.697021484375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.43986892700195</c:v>
+                  <c:v>23.4284725189209</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.047469139099121</c:v>
+                  <c:v>9.043070793151856</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.862771511077881</c:v>
+                  <c:v>3.863753318786621</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.170333862304688</c:v>
+                  <c:v>3.168792486190796</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5608171820640564</c:v>
+                  <c:v>0.5605445504188538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5522332787513733</c:v>
+                  <c:v>0.5519647598266602</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1745400428771973</c:v>
+                  <c:v>0.1744551807641983</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1716787368059158</c:v>
+                  <c:v>0.1715952605009079</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1030072420835495</c:v>
+                  <c:v>0.102957159280777</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0658101812005043</c:v>
+                  <c:v>0.06577818095684052</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.03433574736118317</c:v>
+                  <c:v>0.04575873538851738</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01716787368059158</c:v>
+                  <c:v>0.03431905433535576</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01716787368059158</c:v>
+                  <c:v>0.01715952716767788</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01144524849951267</c:v>
+                  <c:v>0.01715952716767788</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01144524849951267</c:v>
+                  <c:v>0.01143968384712935</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01144524849951267</c:v>
+                  <c:v>0.01143968384712935</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.01144524849951267</c:v>
+                  <c:v>0.01143968384712935</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.005722624249756336</c:v>
+                  <c:v>0.01143968384712935</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.005722624249756336</c:v>
-                </c:pt>
-                <c:pt idx="75">
+                  <c:v>0.005719841923564673</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.005719841923564673</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -565,9 +574,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$78</c:f>
+              <c:f>flash_percent!$A$3:$A$79</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
                   <c:v>usart_app.o</c:v>
                 </c:pt>
@@ -584,10 +593,10 @@
                   <c:v>mc_w.l</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>mcu_cmic_gd32f470vet6.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>ota_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>mcu_cmic_gd32f470vet6.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>printfa.o</c:v>
@@ -611,37 +620,37 @@
                   <c:v>sd_app.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>gd32f4xx_rtc.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>gd32f4xx_rcu.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>gd30ad3344.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>gd32f4xx_sdio.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>gd32f4xx_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>gd32f4xx_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>gd32f4xx_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>startup_gd32f450_470.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>gd32f4xx_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>gd32f4xx_rtc.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>gd32f4xx_fmc.o</c:v>
@@ -653,147 +662,150 @@
                   <c:v>dadd.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>gd32f4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>gd32f4xx_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>btn_app.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
+                  <c:v>gd32f4xx_pmu.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>led_app.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>gd32f4xx_misc.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>gd32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>gd32f4xx_dac.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>diskio.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>oled_app.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>scheduler.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
+                  <c:v>gd32f4xx_exti.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>_strtoul.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>perfc_port_default.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>systick.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>ctype_o.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>strtol.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>gd32f4xx_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="54">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="55">
                   <c:v>strstr.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="56">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="60">
                   <c:v>systick_wrapper_ual.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="61">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="62">
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="63">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="64">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="65">
                   <c:v>_chval.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="66">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="67">
                   <c:v>atoi.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="68">
                   <c:v>strchr.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
-                  <c:v>gd32f4xx_pmu.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>strlen.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>entry8a.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>adc_app.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -801,236 +813,239 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$78</c:f>
+              <c:f>flash_percent!$B$3:$B$79</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>14.05118274688721</c:v>
+                  <c:v>13.81703281402588</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.24417781829834</c:v>
+                  <c:v>11.97681999206543</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.11960029602051</c:v>
+                  <c:v>9.89863395690918</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.995877265930176</c:v>
+                  <c:v>6.843118667602539</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.420161247253418</c:v>
+                  <c:v>6.279973983764648</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.572299003601074</c:v>
+                  <c:v>4.970207691192627</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.379155158996582</c:v>
+                  <c:v>4.472460269927979</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.368012428283691</c:v>
+                  <c:v>4.272634983062744</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.547152996063232</c:v>
+                  <c:v>3.469699144363403</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.203580617904663</c:v>
+                  <c:v>3.133628845214844</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.47743558883667</c:v>
+                  <c:v>2.423339605331421</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.050291538238525</c:v>
+                  <c:v>2.00552248954773</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.582290291786194</c:v>
+                  <c:v>1.54774010181427</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.574861645698547</c:v>
+                  <c:v>1.540473818778992</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.36686110496521</c:v>
+                  <c:v>1.344281315803528</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.363146781921387</c:v>
+                  <c:v>1.33701491355896</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.18857479095459</c:v>
+                  <c:v>1.333381772041321</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.125431776046753</c:v>
+                  <c:v>1.162621736526489</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.092003107070923</c:v>
+                  <c:v>1.100857377052307</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.9991456866264343</c:v>
+                  <c:v>1.068158745765686</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9954314231872559</c:v>
+                  <c:v>0.977328896522522</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9842885136604309</c:v>
+                  <c:v>0.973695695400238</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.8617167472839356</c:v>
+                  <c:v>0.9627960920333862</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8134309053421021</c:v>
+                  <c:v>0.8429007530212402</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.780002236366272</c:v>
+                  <c:v>0.7956692576408386</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7577164769172669</c:v>
+                  <c:v>0.7411713600158691</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.683430552482605</c:v>
+                  <c:v>0.66850745677948</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6202874779701233</c:v>
+                  <c:v>0.6067432165145874</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5237157940864563</c:v>
+                  <c:v>0.5159133672714233</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5237157940864563</c:v>
+                  <c:v>0.5122801661491394</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5237157940864563</c:v>
+                  <c:v>0.5122801661491394</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.4531441628932953</c:v>
+                  <c:v>0.5122801661491394</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4494298696517944</c:v>
+                  <c:v>0.486847847700119</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4420012533664703</c:v>
+                  <c:v>0.443249523639679</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4234297871589661</c:v>
+                  <c:v>0.439616322517395</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4160012006759644</c:v>
+                  <c:v>0.4141839742660523</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4122868776321411</c:v>
+                  <c:v>0.4069176018238068</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3937154114246368</c:v>
+                  <c:v>0.4032844007015228</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3862868249416351</c:v>
+                  <c:v>0.3851184546947479</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3454295694828033</c:v>
+                  <c:v>0.3778520524501801</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3417152762413025</c:v>
+                  <c:v>0.3378869295120239</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.2934294044971466</c:v>
+                  <c:v>0.33425372838974</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.2897151112556458</c:v>
+                  <c:v>0.3051882088184357</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2637150287628174</c:v>
+                  <c:v>0.2870222330093384</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2618578970432282</c:v>
+                  <c:v>0.2833890318870544</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2080006003379822</c:v>
+                  <c:v>0.2579566836357117</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.1894291192293167</c:v>
+                  <c:v>0.2561400830745697</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1820005178451538</c:v>
+                  <c:v>0.2034588009119034</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1820005178451538</c:v>
+                  <c:v>0.1852928400039673</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.08914311230182648</c:v>
+                  <c:v>0.1780264526605606</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.08914311230182648</c:v>
+                  <c:v>0.1780264526605606</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.08171451836824417</c:v>
+                  <c:v>0.08719662576913834</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.07057163119316101</c:v>
+                  <c:v>0.08719662576913834</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.07993024587631226</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.06903066486120224</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.06685733050107956</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.05942874029278755</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.05942874029278755</c:v>
+                  <c:v>0.0653974711894989</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.0557144433259964</c:v>
+                  <c:v>0.05813108384609222</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.0557144433259964</c:v>
+                  <c:v>0.05813108384609222</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.05200015008449554</c:v>
+                  <c:v>0.05449789389967918</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.04828585311770439</c:v>
+                  <c:v>0.05449789389967918</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.04828585311770439</c:v>
+                  <c:v>0.05086470022797585</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.03714296221733093</c:v>
+                  <c:v>0.04723150655627251</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.03342866525053978</c:v>
+                  <c:v>0.04723150655627251</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.02600007504224777</c:v>
+                  <c:v>0.03633192926645279</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02228577807545662</c:v>
+                  <c:v>0.02543235011398792</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.01485718507319689</c:v>
+                  <c:v>0.02179915644228458</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01485718507319689</c:v>
+                  <c:v>0.01453277096152306</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.007428592536598444</c:v>
+                  <c:v>0.01453277096152306</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.007428592536598444</c:v>
+                  <c:v>0.007266385480761528</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.003714296268299222</c:v>
+                  <c:v>0.007266385480761528</c:v>
                 </c:pt>
                 <c:pt idx="75">
+                  <c:v>0.003633192740380764</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1135,8 +1150,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H79" totalsRowCount="1">
+  <autoFilter ref="A2:H78"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1152,8 +1167,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H79" totalsRowCount="1">
+  <autoFilter ref="A2:H78"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1453,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1466,28 +1481,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1495,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>58.72557067871094</v>
+        <v>58.697021484375</v>
       </c>
       <c r="C3" s="1">
         <v>20524</v>
@@ -1521,7 +1536,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>23.43986892700195</v>
+        <v>23.4284725189209</v>
       </c>
       <c r="C4" s="1">
         <v>8192</v>
@@ -1547,16 +1562,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>9.047469139099121</v>
+        <v>9.043070793151856</v>
       </c>
       <c r="C5" s="1">
         <v>3162</v>
       </c>
       <c r="D5" s="1">
-        <v>2358</v>
+        <v>2736</v>
       </c>
       <c r="E5" s="1">
-        <v>2356</v>
+        <v>2734</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1573,16 +1588,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>3.862771511077881</v>
+        <v>3.863753318786621</v>
       </c>
       <c r="C6" s="1">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D6" s="1">
-        <v>7566</v>
+        <v>7606</v>
       </c>
       <c r="E6" s="1">
-        <v>7362</v>
+        <v>7402</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>
@@ -1591,7 +1606,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="1">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1599,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.170333862304688</v>
+        <v>3.168792486190796</v>
       </c>
       <c r="C7" s="1">
         <v>1108</v>
@@ -1625,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.5608171820640564</v>
+        <v>0.5605445504188538</v>
       </c>
       <c r="C8" s="1">
         <v>196</v>
@@ -1651,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5522332787513733</v>
+        <v>0.5519647598266602</v>
       </c>
       <c r="C9" s="1">
         <v>193</v>
@@ -1677,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1745400428771973</v>
+        <v>0.1744551807641983</v>
       </c>
       <c r="C10" s="1">
         <v>61</v>
@@ -1703,7 +1718,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1716787368059158</v>
+        <v>0.1715952605009079</v>
       </c>
       <c r="C11" s="1">
         <v>60</v>
@@ -1729,7 +1744,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1030072420835495</v>
+        <v>0.102957159280777</v>
       </c>
       <c r="C12" s="1">
         <v>36</v>
@@ -1755,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0658101812005043</v>
+        <v>0.06577818095684052</v>
       </c>
       <c r="C13" s="1">
         <v>23</v>
@@ -1781,25 +1796,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.03433574736118317</v>
+        <v>0.04575873538851738</v>
       </c>
       <c r="C14" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="E14" s="1">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1807,25 +1822,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.01716787368059158</v>
+        <v>0.03431905433535576</v>
       </c>
       <c r="C15" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1">
-        <v>734</v>
+        <v>244</v>
       </c>
       <c r="E15" s="1">
-        <v>734</v>
+        <v>242</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1833,19 +1848,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01716787368059158</v>
+        <v>0.01715952716767788</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
       </c>
       <c r="D16" s="1">
-        <v>5449</v>
+        <v>734</v>
       </c>
       <c r="E16" s="1">
-        <v>5308</v>
+        <v>734</v>
       </c>
       <c r="F16" s="1">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -1859,25 +1874,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01144524849951267</v>
+        <v>0.01715952716767788</v>
       </c>
       <c r="C17" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1">
-        <v>3457</v>
+        <v>5449</v>
       </c>
       <c r="E17" s="1">
-        <v>3320</v>
+        <v>5308</v>
       </c>
       <c r="F17" s="1">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1885,19 +1900,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01144524849951267</v>
+        <v>0.01143968384712935</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>12</v>
+        <v>3457</v>
       </c>
       <c r="E18" s="1">
-        <v>8</v>
+        <v>3320</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G18" s="1">
         <v>4</v>
@@ -1911,25 +1926,25 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01144524849951267</v>
+        <v>0.01143968384712935</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="1">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1937,25 +1952,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.01144524849951267</v>
+        <v>0.01143968384712935</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="1">
-        <v>588</v>
+        <v>142</v>
       </c>
       <c r="E20" s="1">
-        <v>584</v>
+        <v>142</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
         <v>4</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1963,25 +1978,25 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.005722624249756336</v>
+        <v>0.01143968384712935</v>
       </c>
       <c r="C21" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>208</v>
+        <v>588</v>
       </c>
       <c r="E21" s="1">
-        <v>186</v>
+        <v>584</v>
       </c>
       <c r="F21" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1989,56 +2004,82 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.005722624249756336</v>
+        <v>0.005719841923564673</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="1">
+        <v>208</v>
+      </c>
+      <c r="E22" s="1">
+        <v>186</v>
+      </c>
+      <c r="F22" s="1">
+        <v>21</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.005719841923564673</v>
+      </c>
+      <c r="C23" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="1">
+      <c r="D23" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="E23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C79">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D79">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E79">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F79">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G79">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H79">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2054,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2067,28 +2108,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" t="s">
         <v>85</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2096,16 +2137,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>14.05118274688721</v>
+        <v>13.81703281402588</v>
       </c>
       <c r="C3" s="1">
-        <v>7566</v>
+        <v>7606</v>
       </c>
       <c r="D3" s="1">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E3" s="1">
-        <v>7362</v>
+        <v>7402</v>
       </c>
       <c r="F3" s="1">
         <v>200</v>
@@ -2114,7 +2155,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="1">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2122,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>12.24417781829834</v>
+        <v>11.97681999206543</v>
       </c>
       <c r="C4" s="1">
         <v>6593</v>
@@ -2145,10 +2186,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>10.11960029602051</v>
+        <v>9.89863395690918</v>
       </c>
       <c r="C5" s="1">
         <v>5449</v>
@@ -2174,7 +2215,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>6.995877265930176</v>
+        <v>6.843118667602539</v>
       </c>
       <c r="C6" s="1">
         <v>3767</v>
@@ -2197,10 +2238,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>6.420161247253418</v>
+        <v>6.279973983764648</v>
       </c>
       <c r="C7" s="1">
         <v>3457</v>
@@ -2223,62 +2264,62 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.572299003601074</v>
+        <v>4.970207691192627</v>
       </c>
       <c r="C8" s="1">
-        <v>2462</v>
+        <v>2736</v>
       </c>
       <c r="D8" s="1">
-        <v>20524</v>
+        <v>3162</v>
       </c>
       <c r="E8" s="1">
-        <v>2462</v>
+        <v>2734</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>20524</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.379155158996582</v>
+        <v>4.472460269927979</v>
       </c>
       <c r="C9" s="1">
-        <v>2358</v>
+        <v>2462</v>
       </c>
       <c r="D9" s="1">
-        <v>3162</v>
+        <v>20524</v>
       </c>
       <c r="E9" s="1">
-        <v>2356</v>
+        <v>2462</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>3160</v>
+        <v>20524</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>4.368012428283691</v>
+        <v>4.272634983062744</v>
       </c>
       <c r="C10" s="1">
         <v>2352</v>
@@ -2304,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.547152996063232</v>
+        <v>3.469699144363403</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2327,10 +2368,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>3.203580617904663</v>
+        <v>3.133628845214844</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2353,10 +2394,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2">
-        <v>2.47743558883667</v>
+        <v>2.423339605331421</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2379,10 +2420,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>2.050291538238525</v>
+        <v>2.00552248954773</v>
       </c>
       <c r="C14" s="1">
         <v>1104</v>
@@ -2408,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.582290291786194</v>
+        <v>1.54774010181427</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2434,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.574861645698547</v>
+        <v>1.540473818778992</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2457,19 +2498,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>1.36686110496521</v>
+        <v>1.344281315803528</v>
       </c>
       <c r="C17" s="1">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2483,19 +2524,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1.363146781921387</v>
+        <v>1.33701491355896</v>
       </c>
       <c r="C18" s="1">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D18" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2504,24 +2545,24 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2">
-        <v>1.18857479095459</v>
+        <v>1.333381772041321</v>
       </c>
       <c r="C19" s="1">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1">
-        <v>640</v>
+        <v>734</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2530,24 +2571,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2">
-        <v>1.125431776046753</v>
+        <v>1.162621736526489</v>
       </c>
       <c r="C20" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2561,25 +2602,25 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2">
-        <v>1.092003107070923</v>
+        <v>1.100857377052307</v>
       </c>
       <c r="C21" s="1">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="D21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -2587,25 +2628,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2">
-        <v>0.9991456866264343</v>
+        <v>1.068158745765686</v>
       </c>
       <c r="C22" s="1">
-        <v>538</v>
+        <v>588</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1">
-        <v>538</v>
+        <v>584</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2613,19 +2654,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9954314231872559</v>
+        <v>0.977328896522522</v>
       </c>
       <c r="C23" s="1">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2639,19 +2680,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2">
-        <v>0.9842885136604309</v>
+        <v>0.973695695400238</v>
       </c>
       <c r="C24" s="1">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2665,71 +2706,71 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2">
-        <v>0.8617167472839356</v>
+        <v>0.9627960920333862</v>
       </c>
       <c r="C25" s="1">
-        <v>464</v>
+        <v>530</v>
       </c>
       <c r="D25" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>36</v>
+        <v>530</v>
       </c>
       <c r="F25" s="1">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>8192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8134309053421021</v>
+        <v>0.8429007530212402</v>
       </c>
       <c r="C26" s="1">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
       <c r="E26" s="1">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.780002236366272</v>
+        <v>0.7956692576408386</v>
       </c>
       <c r="C27" s="1">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2743,10 +2784,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7577164769172669</v>
+        <v>0.7411713600158691</v>
       </c>
       <c r="C28" s="1">
         <v>408</v>
@@ -2769,10 +2810,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.683430552482605</v>
+        <v>0.66850745677948</v>
       </c>
       <c r="C29" s="1">
         <v>368</v>
@@ -2795,10 +2836,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6202874779701233</v>
+        <v>0.6067432165145874</v>
       </c>
       <c r="C30" s="1">
         <v>334</v>
@@ -2821,19 +2862,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5237157940864563</v>
+        <v>0.5159133672714233</v>
       </c>
       <c r="C31" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2847,10 +2888,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5237157940864563</v>
+        <v>0.5122801661491394</v>
       </c>
       <c r="C32" s="1">
         <v>282</v>
@@ -2873,71 +2914,71 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5237157940864563</v>
+        <v>0.5122801661491394</v>
       </c>
       <c r="C33" s="1">
         <v>282</v>
       </c>
       <c r="D33" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F33" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.4531441628932953</v>
+        <v>0.5122801661491394</v>
       </c>
       <c r="C34" s="1">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="D34" s="1">
-        <v>12</v>
+        <v>196</v>
       </c>
       <c r="E34" s="1">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>10</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4494298696517944</v>
+        <v>0.486847847700119</v>
       </c>
       <c r="C35" s="1">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E35" s="1">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -2946,33 +2987,33 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4420012533664703</v>
+        <v>0.443249523639679</v>
       </c>
       <c r="C36" s="1">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -2980,16 +3021,16 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4234297871589661</v>
+        <v>0.439616322517395</v>
       </c>
       <c r="C37" s="1">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3006,16 +3047,16 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4160012006759644</v>
+        <v>0.4141839742660523</v>
       </c>
       <c r="C38" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -3032,16 +3073,16 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4122868776321411</v>
+        <v>0.4069176018238068</v>
       </c>
       <c r="C39" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -3058,16 +3099,16 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3937154114246368</v>
+        <v>0.4032844007015228</v>
       </c>
       <c r="C40" s="1">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3081,71 +3122,71 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3862868249416351</v>
+        <v>0.3851184546947479</v>
       </c>
       <c r="C41" s="1">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D41" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="F41" s="1">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3454295694828033</v>
+        <v>0.3778520524501801</v>
       </c>
       <c r="C42" s="1">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="1">
         <v>186</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3417152762413025</v>
+        <v>0.3378869295120239</v>
       </c>
       <c r="C43" s="1">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D43" s="1">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3154,24 +3195,24 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2">
-        <v>0.2934294044971466</v>
+        <v>0.33425372838974</v>
       </c>
       <c r="C44" s="1">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="E44" s="1">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3180,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -3188,16 +3229,16 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.2897151112556458</v>
+        <v>0.3051882088184357</v>
       </c>
       <c r="C45" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3211,19 +3252,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2637150287628174</v>
+        <v>0.2870222330093384</v>
       </c>
       <c r="C46" s="1">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3232,27 +3273,27 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2618578970432282</v>
+        <v>0.2833890318870544</v>
       </c>
       <c r="C47" s="1">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="F47" s="1">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
@@ -3263,19 +3304,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2080006003379822</v>
+        <v>0.2579566836357117</v>
       </c>
       <c r="C48" s="1">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3284,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3292,19 +3333,19 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.1894291192293167</v>
+        <v>0.2561400830745697</v>
       </c>
       <c r="C49" s="1">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
@@ -3318,16 +3359,16 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1820005178451538</v>
+        <v>0.2034588009119034</v>
       </c>
       <c r="C50" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3344,16 +3385,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1820005178451538</v>
+        <v>0.1852928400039673</v>
       </c>
       <c r="C51" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3370,16 +3411,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.08914311230182648</v>
+        <v>0.1780264526605606</v>
       </c>
       <c r="C52" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3396,16 +3437,16 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.08914311230182648</v>
+        <v>0.1780264526605606</v>
       </c>
       <c r="C53" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3422,16 +3463,16 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.08171451836824417</v>
+        <v>0.08719662576913834</v>
       </c>
       <c r="C54" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3448,16 +3489,16 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.07057163119316101</v>
+        <v>0.08719662576913834</v>
       </c>
       <c r="C55" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3474,16 +3515,16 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.07993024587631226</v>
       </c>
       <c r="C56" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3500,16 +3541,16 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.06903066486120224</v>
       </c>
       <c r="C57" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3526,7 +3567,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3552,7 +3593,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3578,7 +3619,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3604,7 +3645,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.06685733050107956</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C61" s="1">
         <v>36</v>
@@ -3630,16 +3671,16 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.05942874029278755</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C62" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3656,16 +3697,16 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.05942874029278755</v>
+        <v>0.0653974711894989</v>
       </c>
       <c r="C63" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3682,16 +3723,16 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.0557144433259964</v>
+        <v>0.05813108384609222</v>
       </c>
       <c r="C64" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3708,16 +3749,16 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.0557144433259964</v>
+        <v>0.05813108384609222</v>
       </c>
       <c r="C65" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3734,16 +3775,16 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.05200015008449554</v>
+        <v>0.05449789389967918</v>
       </c>
       <c r="C66" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3760,16 +3801,16 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.04828585311770439</v>
+        <v>0.05449789389967918</v>
       </c>
       <c r="C67" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3786,16 +3827,16 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.04828585311770439</v>
+        <v>0.05086470022797585</v>
       </c>
       <c r="C68" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3812,16 +3853,16 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.03714296221733093</v>
+        <v>0.04723150655627251</v>
       </c>
       <c r="C69" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3838,16 +3879,16 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.03342866525053978</v>
+        <v>0.04723150655627251</v>
       </c>
       <c r="C70" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -3864,16 +3905,16 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.02600007504224777</v>
+        <v>0.03633192926645279</v>
       </c>
       <c r="C71" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -3887,25 +3928,25 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02228577807545662</v>
+        <v>0.02543235011398792</v>
       </c>
       <c r="C72" s="1">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -3913,16 +3954,16 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B73" s="2">
-        <v>0.01485718507319689</v>
+        <v>0.02179915644228458</v>
       </c>
       <c r="C73" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E73" s="1">
         <v>8</v>
@@ -3931,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3942,7 +3983,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01485718507319689</v>
+        <v>0.01453277096152306</v>
       </c>
       <c r="C74" s="1">
         <v>8</v>
@@ -3968,16 +4009,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.007428592536598444</v>
+        <v>0.01453277096152306</v>
       </c>
       <c r="C75" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -3994,7 +4035,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.007428592536598444</v>
+        <v>0.007266385480761528</v>
       </c>
       <c r="C76" s="1">
         <v>4</v>
@@ -4017,59 +4058,85 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.003714296268299222</v>
+        <v>0.007266385480761528</v>
       </c>
       <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>4</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.003633192740380764</v>
+      </c>
+      <c r="C78" s="1">
         <v>2</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D78" s="1">
         <v>2</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E78" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C79">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D79">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E79">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F79">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G79">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H79">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -128,10 +128,10 @@
     <t>dadd.o</t>
   </si>
   <si>
+    <t>main.o</t>
+  </si>
+  <si>
     <t>gd32f4xx_it.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
   </si>
   <si>
     <t>gd32f4xx_gpio.o</t>
@@ -444,67 +444,67 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>58.697021484375</c:v>
+                  <c:v>58.68862915039063</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.4284725189209</c:v>
+                  <c:v>23.42512321472168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.043070793151856</c:v>
+                  <c:v>9.041777610778809</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.863753318786621</c:v>
+                  <c:v>3.877498388290405</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.168792486190796</c:v>
+                  <c:v>3.168339490890503</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5605445504188538</c:v>
+                  <c:v>0.5604643821716309</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5519647598266602</c:v>
+                  <c:v>0.5518858432769775</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1744551807641983</c:v>
+                  <c:v>0.1744302362203598</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1715952605009079</c:v>
+                  <c:v>0.1715707331895828</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.102957159280777</c:v>
+                  <c:v>0.1029424369335175</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.06577818095684052</c:v>
+                  <c:v>0.0657687783241272</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.04575873538851738</c:v>
+                  <c:v>0.04575219377875328</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.03431905433535576</c:v>
+                  <c:v>0.03431414440274239</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01715952716767788</c:v>
+                  <c:v>0.01715707220137119</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01715952716767788</c:v>
+                  <c:v>0.01715707220137119</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01143968384712935</c:v>
+                  <c:v>0.01143804844468832</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.01143968384712935</c:v>
+                  <c:v>0.01143804844468832</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.01143968384712935</c:v>
+                  <c:v>0.01143804844468832</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.01143968384712935</c:v>
+                  <c:v>0.01143804844468832</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.005719841923564673</c:v>
+                  <c:v>0.00571902422234416</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.005719841923564673</c:v>
+                  <c:v>0.00571902422234416</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -662,10 +662,10 @@
                   <c:v>dadd.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>gd32f4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>gd32f4xx_gpio.o</c:v>
@@ -818,232 +818,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>13.81703281402588</c:v>
+                  <c:v>15.13018035888672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.97681999206543</c:v>
+                  <c:v>11.781418800354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.89863395690918</c:v>
+                  <c:v>9.737138748168945</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.843118667602539</c:v>
+                  <c:v>6.731473922729492</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.279973983764648</c:v>
+                  <c:v>6.177516460418701</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.970207691192627</c:v>
+                  <c:v>4.924858570098877</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.472460269927979</c:v>
+                  <c:v>4.399492740631104</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.272634983062744</c:v>
+                  <c:v>4.202927112579346</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.469699144363403</c:v>
+                  <c:v>3.41309118270874</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.133628845214844</c:v>
+                  <c:v>3.082503795623779</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.423339605331421</c:v>
+                  <c:v>2.383802890777588</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.00552248954773</c:v>
+                  <c:v>1.972802519798279</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.54774010181427</c:v>
+                  <c:v>1.522488832473755</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.540473818778992</c:v>
+                  <c:v>1.51534104347229</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.344281315803528</c:v>
+                  <c:v>1.322349548339844</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.33701491355896</c:v>
+                  <c:v>1.315201640129089</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.333381772041321</c:v>
+                  <c:v>1.311627745628357</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.162621736526489</c:v>
+                  <c:v>1.143653631210327</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.100857377052307</c:v>
+                  <c:v>1.082897067070007</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.068158745765686</c:v>
+                  <c:v>1.050731778144836</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.977328896522522</c:v>
+                  <c:v>0.9613838195800781</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.973695695400238</c:v>
+                  <c:v>0.9578099250793457</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9627960920333862</c:v>
+                  <c:v>0.9470881223678589</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8429007530212402</c:v>
+                  <c:v>0.8291488885879517</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.7956692576408386</c:v>
+                  <c:v>0.7826879620552063</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7411713600158691</c:v>
+                  <c:v>0.7290791869163513</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.66850745677948</c:v>
+                  <c:v>0.6576008200645447</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.6067432165145874</c:v>
+                  <c:v>0.5968442559242249</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5159133672714233</c:v>
+                  <c:v>0.5325137376785278</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5122801661491394</c:v>
+                  <c:v>0.5074962973594666</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5122801661491394</c:v>
+                  <c:v>0.5039224028587341</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.5122801661491394</c:v>
+                  <c:v>0.5039224028587341</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.486847847700119</c:v>
+                  <c:v>0.4789049625396729</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.443249523639679</c:v>
+                  <c:v>0.4360179305076599</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.439616322517395</c:v>
+                  <c:v>0.4324440360069275</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4141839742660523</c:v>
+                  <c:v>0.4074265956878662</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.4069176018238068</c:v>
+                  <c:v>0.400278776884079</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.4032844007015228</c:v>
+                  <c:v>0.3967048525810242</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3851184546947479</c:v>
+                  <c:v>0.3788352608680725</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3778520524501801</c:v>
+                  <c:v>0.3716874122619629</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3378869295120239</c:v>
+                  <c:v>0.3323743343353272</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.33425372838974</c:v>
+                  <c:v>0.3288004100322723</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3051882088184357</c:v>
+                  <c:v>0.3288004100322723</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2870222330093384</c:v>
+                  <c:v>0.282339483499527</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2833890318870544</c:v>
+                  <c:v>0.2787655591964722</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2579566836357117</c:v>
+                  <c:v>0.2537481486797333</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2561400830745697</c:v>
+                  <c:v>0.2519612014293671</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2034588009119034</c:v>
+                  <c:v>0.2001393884420395</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1852928400039673</c:v>
+                  <c:v>0.1822697967290878</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1780264526605606</c:v>
+                  <c:v>0.1751219630241394</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1780264526605606</c:v>
+                  <c:v>0.1751219630241394</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.08719662576913834</c:v>
+                  <c:v>0.0857740193605423</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.08719662576913834</c:v>
+                  <c:v>0.0857740193605423</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.07993024587631226</c:v>
+                  <c:v>0.07862618565559387</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06903066486120224</c:v>
+                  <c:v>0.06790443509817123</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.0653974711894989</c:v>
+                  <c:v>0.06433051824569702</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.05813108384609222</c:v>
+                  <c:v>0.0571826808154583</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.05813108384609222</c:v>
+                  <c:v>0.0571826808154583</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.05449789389967918</c:v>
+                  <c:v>0.05360876396298409</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.05449789389967918</c:v>
+                  <c:v>0.05360876396298409</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.05086470022797585</c:v>
+                  <c:v>0.05003484711050987</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.04723150655627251</c:v>
+                  <c:v>0.04646092653274536</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.04723150655627251</c:v>
+                  <c:v>0.04646092653274536</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.03633192926645279</c:v>
+                  <c:v>0.03573917597532272</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02543235011398792</c:v>
+                  <c:v>0.02501742355525494</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02179915644228458</c:v>
+                  <c:v>0.02144350484013557</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01453277096152306</c:v>
+                  <c:v>0.01429567020386457</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01453277096152306</c:v>
+                  <c:v>0.01429567020386457</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.007266385480761528</c:v>
+                  <c:v>0.007147835101932287</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.007266385480761528</c:v>
+                  <c:v>0.007147835101932287</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.003633192740380764</c:v>
+                  <c:v>0.003573917550966144</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>58.697021484375</v>
+        <v>58.68862915039063</v>
       </c>
       <c r="C3" s="1">
         <v>20524</v>
@@ -1536,7 +1536,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>23.4284725189209</v>
+        <v>23.42512321472168</v>
       </c>
       <c r="C4" s="1">
         <v>8192</v>
@@ -1562,16 +1562,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>9.043070793151856</v>
+        <v>9.041777610778809</v>
       </c>
       <c r="C5" s="1">
         <v>3162</v>
       </c>
       <c r="D5" s="1">
-        <v>2736</v>
+        <v>2756</v>
       </c>
       <c r="E5" s="1">
-        <v>2734</v>
+        <v>2754</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1588,25 +1588,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>3.863753318786621</v>
+        <v>3.877498388290405</v>
       </c>
       <c r="C6" s="1">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="D6" s="1">
-        <v>7606</v>
+        <v>8467</v>
       </c>
       <c r="E6" s="1">
-        <v>7402</v>
+        <v>8262</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="1">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1614,7 +1614,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.168792486190796</v>
+        <v>3.168339490890503</v>
       </c>
       <c r="C7" s="1">
         <v>1108</v>
@@ -1640,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.5605445504188538</v>
+        <v>0.5604643821716309</v>
       </c>
       <c r="C8" s="1">
         <v>196</v>
@@ -1666,7 +1666,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5519647598266602</v>
+        <v>0.5518858432769775</v>
       </c>
       <c r="C9" s="1">
         <v>193</v>
@@ -1692,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1744551807641983</v>
+        <v>0.1744302362203598</v>
       </c>
       <c r="C10" s="1">
         <v>61</v>
@@ -1718,7 +1718,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1715952605009079</v>
+        <v>0.1715707331895828</v>
       </c>
       <c r="C11" s="1">
         <v>60</v>
@@ -1744,7 +1744,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.102957159280777</v>
+        <v>0.1029424369335175</v>
       </c>
       <c r="C12" s="1">
         <v>36</v>
@@ -1770,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.06577818095684052</v>
+        <v>0.0657687783241272</v>
       </c>
       <c r="C13" s="1">
         <v>23</v>
@@ -1796,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.04575873538851738</v>
+        <v>0.04575219377875328</v>
       </c>
       <c r="C14" s="1">
         <v>16</v>
@@ -1822,7 +1822,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.03431905433535576</v>
+        <v>0.03431414440274239</v>
       </c>
       <c r="C15" s="1">
         <v>12</v>
@@ -1848,7 +1848,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.01715952716767788</v>
+        <v>0.01715707220137119</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
@@ -1874,7 +1874,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01715952716767788</v>
+        <v>0.01715707220137119</v>
       </c>
       <c r="C17" s="1">
         <v>6</v>
@@ -1900,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01143968384712935</v>
+        <v>0.01143804844468832</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
@@ -1926,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.01143968384712935</v>
+        <v>0.01143804844468832</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
@@ -1952,7 +1952,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.01143968384712935</v>
+        <v>0.01143804844468832</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
@@ -1978,7 +1978,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.01143968384712935</v>
+        <v>0.01143804844468832</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
@@ -2004,7 +2004,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.005719841923564673</v>
+        <v>0.00571902422234416</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
@@ -2030,7 +2030,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.005719841923564673</v>
+        <v>0.00571902422234416</v>
       </c>
       <c r="C23" s="1">
         <v>2</v>
@@ -2137,25 +2137,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>13.81703281402588</v>
+        <v>15.13018035888672</v>
       </c>
       <c r="C3" s="1">
-        <v>7606</v>
+        <v>8467</v>
       </c>
       <c r="D3" s="1">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="E3" s="1">
-        <v>7402</v>
+        <v>8262</v>
       </c>
       <c r="F3" s="1">
         <v>200</v>
       </c>
       <c r="G3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1">
-        <v>1347</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>11.97681999206543</v>
+        <v>11.781418800354</v>
       </c>
       <c r="C4" s="1">
         <v>6593</v>
@@ -2189,7 +2189,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>9.89863395690918</v>
+        <v>9.737138748168945</v>
       </c>
       <c r="C5" s="1">
         <v>5449</v>
@@ -2215,7 +2215,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>6.843118667602539</v>
+        <v>6.731473922729492</v>
       </c>
       <c r="C6" s="1">
         <v>3767</v>
@@ -2241,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>6.279973983764648</v>
+        <v>6.177516460418701</v>
       </c>
       <c r="C7" s="1">
         <v>3457</v>
@@ -2267,16 +2267,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.970207691192627</v>
+        <v>4.924858570098877</v>
       </c>
       <c r="C8" s="1">
-        <v>2736</v>
+        <v>2756</v>
       </c>
       <c r="D8" s="1">
         <v>3162</v>
       </c>
       <c r="E8" s="1">
-        <v>2734</v>
+        <v>2754</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.472460269927979</v>
+        <v>4.399492740631104</v>
       </c>
       <c r="C9" s="1">
         <v>2462</v>
@@ -2319,7 +2319,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>4.272634983062744</v>
+        <v>4.202927112579346</v>
       </c>
       <c r="C10" s="1">
         <v>2352</v>
@@ -2345,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.469699144363403</v>
+        <v>3.41309118270874</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2371,7 +2371,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>3.133628845214844</v>
+        <v>3.082503795623779</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2397,7 +2397,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="2">
-        <v>2.423339605331421</v>
+        <v>2.383802890777588</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2423,7 +2423,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>2.00552248954773</v>
+        <v>1.972802519798279</v>
       </c>
       <c r="C14" s="1">
         <v>1104</v>
@@ -2449,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.54774010181427</v>
+        <v>1.522488832473755</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.540473818778992</v>
+        <v>1.51534104347229</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2501,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>1.344281315803528</v>
+        <v>1.322349548339844</v>
       </c>
       <c r="C17" s="1">
         <v>740</v>
@@ -2527,7 +2527,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1.33701491355896</v>
+        <v>1.315201640129089</v>
       </c>
       <c r="C18" s="1">
         <v>736</v>
@@ -2553,7 +2553,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="2">
-        <v>1.333381772041321</v>
+        <v>1.311627745628357</v>
       </c>
       <c r="C19" s="1">
         <v>734</v>
@@ -2579,7 +2579,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="2">
-        <v>1.162621736526489</v>
+        <v>1.143653631210327</v>
       </c>
       <c r="C20" s="1">
         <v>640</v>
@@ -2605,7 +2605,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2">
-        <v>1.100857377052307</v>
+        <v>1.082897067070007</v>
       </c>
       <c r="C21" s="1">
         <v>606</v>
@@ -2631,7 +2631,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2">
-        <v>1.068158745765686</v>
+        <v>1.050731778144836</v>
       </c>
       <c r="C22" s="1">
         <v>588</v>
@@ -2657,7 +2657,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="2">
-        <v>0.977328896522522</v>
+        <v>0.9613838195800781</v>
       </c>
       <c r="C23" s="1">
         <v>538</v>
@@ -2683,7 +2683,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="2">
-        <v>0.973695695400238</v>
+        <v>0.9578099250793457</v>
       </c>
       <c r="C24" s="1">
         <v>536</v>
@@ -2709,7 +2709,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9627960920333862</v>
+        <v>0.9470881223678589</v>
       </c>
       <c r="C25" s="1">
         <v>530</v>
@@ -2735,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8429007530212402</v>
+        <v>0.8291488885879517</v>
       </c>
       <c r="C26" s="1">
         <v>464</v>
@@ -2761,7 +2761,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.7956692576408386</v>
+        <v>0.7826879620552063</v>
       </c>
       <c r="C27" s="1">
         <v>438</v>
@@ -2787,7 +2787,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7411713600158691</v>
+        <v>0.7290791869163513</v>
       </c>
       <c r="C28" s="1">
         <v>408</v>
@@ -2813,7 +2813,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.66850745677948</v>
+        <v>0.6576008200645447</v>
       </c>
       <c r="C29" s="1">
         <v>368</v>
@@ -2839,7 +2839,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="2">
-        <v>0.6067432165145874</v>
+        <v>0.5968442559242249</v>
       </c>
       <c r="C30" s="1">
         <v>334</v>
@@ -2865,16 +2865,16 @@
         <v>37</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5159133672714233</v>
+        <v>0.5325137376785278</v>
       </c>
       <c r="C31" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2891,16 +2891,16 @@
         <v>38</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5122801661491394</v>
+        <v>0.5074962973594666</v>
       </c>
       <c r="C32" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5122801661491394</v>
+        <v>0.5039224028587341</v>
       </c>
       <c r="C33" s="1">
         <v>282</v>
@@ -2943,7 +2943,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.5122801661491394</v>
+        <v>0.5039224028587341</v>
       </c>
       <c r="C34" s="1">
         <v>282</v>
@@ -2969,7 +2969,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>0.486847847700119</v>
+        <v>0.4789049625396729</v>
       </c>
       <c r="C35" s="1">
         <v>268</v>
@@ -2995,7 +2995,7 @@
         <v>13</v>
       </c>
       <c r="B36" s="2">
-        <v>0.443249523639679</v>
+        <v>0.4360179305076599</v>
       </c>
       <c r="C36" s="1">
         <v>244</v>
@@ -3021,7 +3021,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.439616322517395</v>
+        <v>0.4324440360069275</v>
       </c>
       <c r="C37" s="1">
         <v>242</v>
@@ -3047,7 +3047,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4141839742660523</v>
+        <v>0.4074265956878662</v>
       </c>
       <c r="C38" s="1">
         <v>228</v>
@@ -3073,7 +3073,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.4069176018238068</v>
+        <v>0.400278776884079</v>
       </c>
       <c r="C39" s="1">
         <v>224</v>
@@ -3099,7 +3099,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.4032844007015228</v>
+        <v>0.3967048525810242</v>
       </c>
       <c r="C40" s="1">
         <v>222</v>
@@ -3125,7 +3125,7 @@
         <v>44</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3851184546947479</v>
+        <v>0.3788352608680725</v>
       </c>
       <c r="C41" s="1">
         <v>212</v>
@@ -3151,7 +3151,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3778520524501801</v>
+        <v>0.3716874122619629</v>
       </c>
       <c r="C42" s="1">
         <v>208</v>
@@ -3177,7 +3177,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3378869295120239</v>
+        <v>0.3323743343353272</v>
       </c>
       <c r="C43" s="1">
         <v>186</v>
@@ -3203,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="2">
-        <v>0.33425372838974</v>
+        <v>0.3288004100322723</v>
       </c>
       <c r="C44" s="1">
         <v>184</v>
@@ -3229,16 +3229,16 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3051882088184357</v>
+        <v>0.3288004100322723</v>
       </c>
       <c r="C45" s="1">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2870222330093384</v>
+        <v>0.282339483499527</v>
       </c>
       <c r="C46" s="1">
         <v>158</v>
@@ -3281,7 +3281,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2833890318870544</v>
+        <v>0.2787655591964722</v>
       </c>
       <c r="C47" s="1">
         <v>156</v>
@@ -3307,7 +3307,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2579566836357117</v>
+        <v>0.2537481486797333</v>
       </c>
       <c r="C48" s="1">
         <v>142</v>
@@ -3333,7 +3333,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2561400830745697</v>
+        <v>0.2519612014293671</v>
       </c>
       <c r="C49" s="1">
         <v>141</v>
@@ -3359,7 +3359,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2034588009119034</v>
+        <v>0.2001393884420395</v>
       </c>
       <c r="C50" s="1">
         <v>112</v>
@@ -3385,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1852928400039673</v>
+        <v>0.1822697967290878</v>
       </c>
       <c r="C51" s="1">
         <v>102</v>
@@ -3411,7 +3411,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1780264526605606</v>
+        <v>0.1751219630241394</v>
       </c>
       <c r="C52" s="1">
         <v>98</v>
@@ -3437,7 +3437,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1780264526605606</v>
+        <v>0.1751219630241394</v>
       </c>
       <c r="C53" s="1">
         <v>98</v>
@@ -3463,7 +3463,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.08719662576913834</v>
+        <v>0.0857740193605423</v>
       </c>
       <c r="C54" s="1">
         <v>48</v>
@@ -3489,7 +3489,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.08719662576913834</v>
+        <v>0.0857740193605423</v>
       </c>
       <c r="C55" s="1">
         <v>48</v>
@@ -3515,7 +3515,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.07993024587631226</v>
+        <v>0.07862618565559387</v>
       </c>
       <c r="C56" s="1">
         <v>44</v>
@@ -3541,7 +3541,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06903066486120224</v>
+        <v>0.06790443509817123</v>
       </c>
       <c r="C57" s="1">
         <v>38</v>
@@ -3567,7 +3567,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3593,7 +3593,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3619,7 +3619,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3645,7 +3645,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C61" s="1">
         <v>36</v>
@@ -3671,7 +3671,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C62" s="1">
         <v>36</v>
@@ -3697,7 +3697,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.0653974711894989</v>
+        <v>0.06433051824569702</v>
       </c>
       <c r="C63" s="1">
         <v>36</v>
@@ -3723,7 +3723,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.05813108384609222</v>
+        <v>0.0571826808154583</v>
       </c>
       <c r="C64" s="1">
         <v>32</v>
@@ -3749,7 +3749,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.05813108384609222</v>
+        <v>0.0571826808154583</v>
       </c>
       <c r="C65" s="1">
         <v>32</v>
@@ -3775,7 +3775,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.05449789389967918</v>
+        <v>0.05360876396298409</v>
       </c>
       <c r="C66" s="1">
         <v>30</v>
@@ -3801,7 +3801,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.05449789389967918</v>
+        <v>0.05360876396298409</v>
       </c>
       <c r="C67" s="1">
         <v>30</v>
@@ -3827,7 +3827,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.05086470022797585</v>
+        <v>0.05003484711050987</v>
       </c>
       <c r="C68" s="1">
         <v>28</v>
@@ -3853,7 +3853,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.04723150655627251</v>
+        <v>0.04646092653274536</v>
       </c>
       <c r="C69" s="1">
         <v>26</v>
@@ -3879,7 +3879,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.04723150655627251</v>
+        <v>0.04646092653274536</v>
       </c>
       <c r="C70" s="1">
         <v>26</v>
@@ -3905,7 +3905,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.03633192926645279</v>
+        <v>0.03573917597532272</v>
       </c>
       <c r="C71" s="1">
         <v>20</v>
@@ -3931,7 +3931,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02543235011398792</v>
+        <v>0.02501742355525494</v>
       </c>
       <c r="C72" s="1">
         <v>14</v>
@@ -3957,7 +3957,7 @@
         <v>17</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02179915644228458</v>
+        <v>0.02144350484013557</v>
       </c>
       <c r="C73" s="1">
         <v>12</v>
@@ -3983,7 +3983,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01453277096152306</v>
+        <v>0.01429567020386457</v>
       </c>
       <c r="C74" s="1">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01453277096152306</v>
+        <v>0.01429567020386457</v>
       </c>
       <c r="C75" s="1">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.007266385480761528</v>
+        <v>0.007147835101932287</v>
       </c>
       <c r="C76" s="1">
         <v>4</v>
@@ -4061,7 +4061,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.007266385480761528</v>
+        <v>0.007147835101932287</v>
       </c>
       <c r="C77" s="1">
         <v>4</v>
@@ -4087,7 +4087,7 @@
         <v>21</v>
       </c>
       <c r="B78" s="2">
-        <v>0.003633192740380764</v>
+        <v>0.003573917550966144</v>
       </c>
       <c r="C78" s="1">
         <v>2</v>

--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -629,13 +629,13 @@
                   <c:v>gd30ad3344.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>system_gd32f4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>gd32f4xx_sdio.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>gd32f4xx_usart.o</c:v>
@@ -818,232 +818,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>15.13018035888672</c:v>
+                  <c:v>15.08718204498291</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.781418800354</c:v>
+                  <c:v>11.7423906326294</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.737138748168945</c:v>
+                  <c:v>9.70488166809082</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.731473922729492</c:v>
+                  <c:v>6.709174156188965</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.177516460418701</c:v>
+                  <c:v>6.157052040100098</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.924858570098877</c:v>
+                  <c:v>4.983347415924072</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.399492740631104</c:v>
+                  <c:v>4.384918212890625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.202927112579346</c:v>
+                  <c:v>4.189003944396973</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.41309118270874</c:v>
+                  <c:v>3.401784658432007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.082503795623779</c:v>
+                  <c:v>3.072292327880859</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.383802890777588</c:v>
+                  <c:v>2.375905990600586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.972802519798279</c:v>
+                  <c:v>1.966267108917236</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.522488832473755</c:v>
+                  <c:v>1.51744532585144</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.51534104347229</c:v>
+                  <c:v>1.510321140289307</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.322349548339844</c:v>
+                  <c:v>1.317968845367432</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.315201640129089</c:v>
+                  <c:v>1.310844779014587</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.311627745628357</c:v>
+                  <c:v>1.307282686233521</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.143653631210327</c:v>
+                  <c:v>1.29659640789032</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.082897067070007</c:v>
+                  <c:v>1.139865040779114</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.050731778144836</c:v>
+                  <c:v>1.079309701919556</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9613838195800781</c:v>
+                  <c:v>0.9581990242004395</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9578099250793457</c:v>
+                  <c:v>0.9546369314193726</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9470881223678589</c:v>
+                  <c:v>0.9439507126808167</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8291488885879517</c:v>
+                  <c:v>0.8264021277427673</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.7826879620552063</c:v>
+                  <c:v>0.780095100402832</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7290791869163513</c:v>
+                  <c:v>0.7266639471054077</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6576008200645447</c:v>
+                  <c:v>0.6554223895072937</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5968442559242249</c:v>
+                  <c:v>0.5948670506477356</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5325137376785278</c:v>
+                  <c:v>0.5307496190071106</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5074962973594666</c:v>
+                  <c:v>0.5058150887489319</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.5039224028587341</c:v>
+                  <c:v>0.502252995967865</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.5039224028587341</c:v>
+                  <c:v>0.502252995967865</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4789049625396729</c:v>
+                  <c:v>0.4773184657096863</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4360179305076599</c:v>
+                  <c:v>0.4345735311508179</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.4324440360069275</c:v>
+                  <c:v>0.431011438369751</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4074265956878662</c:v>
+                  <c:v>0.4060769081115723</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.400278776884079</c:v>
+                  <c:v>0.3989527523517609</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.3967048525810242</c:v>
+                  <c:v>0.395390659570694</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3788352608680725</c:v>
+                  <c:v>0.3775802850723267</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3716874122619629</c:v>
+                  <c:v>0.3704561293125153</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3323743343353272</c:v>
+                  <c:v>0.3312732577323914</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.3288004100322723</c:v>
+                  <c:v>0.3277111947536469</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3288004100322723</c:v>
+                  <c:v>0.3277111947536469</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.282339483499527</c:v>
+                  <c:v>0.2814041674137116</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.2787655591964722</c:v>
+                  <c:v>0.277842104434967</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2537481486797333</c:v>
+                  <c:v>0.2529075443744659</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2519612014293671</c:v>
+                  <c:v>0.2511264979839325</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2001393884420395</c:v>
+                  <c:v>0.1994763761758804</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1822697967290878</c:v>
+                  <c:v>0.1816659867763519</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1751219630241394</c:v>
+                  <c:v>0.1745418310165405</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1751219630241394</c:v>
+                  <c:v>0.1745418310165405</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.0857740193605423</c:v>
+                  <c:v>0.08548987656831741</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.0857740193605423</c:v>
+                  <c:v>0.08548987656831741</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.07862618565559387</c:v>
+                  <c:v>0.07836572080850601</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06790443509817123</c:v>
+                  <c:v>0.06767948716878891</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.06433051824569702</c:v>
+                  <c:v>0.06411740928888321</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.0571826808154583</c:v>
+                  <c:v>0.05699324980378151</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.0571826808154583</c:v>
+                  <c:v>0.05699324980378151</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.05360876396298409</c:v>
+                  <c:v>0.05343117192387581</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.05360876396298409</c:v>
+                  <c:v>0.05343117192387581</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.05003484711050987</c:v>
+                  <c:v>0.04986909404397011</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.04646092653274536</c:v>
+                  <c:v>0.04630701616406441</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.04646092653274536</c:v>
+                  <c:v>0.04630701616406441</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.03573917597532272</c:v>
+                  <c:v>0.03562078252434731</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02501742355525494</c:v>
+                  <c:v>0.02493454702198505</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02144350484013557</c:v>
+                  <c:v>0.02137246914207935</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01429567020386457</c:v>
+                  <c:v>0.01424831245094538</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01429567020386457</c:v>
+                  <c:v>0.01424831245094538</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.007147835101932287</c:v>
+                  <c:v>0.007124156225472689</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.007147835101932287</c:v>
+                  <c:v>0.007124156225472689</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.003573917550966144</c:v>
+                  <c:v>0.003562078112736344</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -1568,10 +1568,10 @@
         <v>3162</v>
       </c>
       <c r="D5" s="1">
-        <v>2756</v>
+        <v>2798</v>
       </c>
       <c r="E5" s="1">
-        <v>2754</v>
+        <v>2796</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         <v>1356</v>
       </c>
       <c r="D6" s="1">
-        <v>8467</v>
+        <v>8471</v>
       </c>
       <c r="E6" s="1">
-        <v>8262</v>
+        <v>8266</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>
@@ -1984,10 +1984,10 @@
         <v>4</v>
       </c>
       <c r="D21" s="1">
-        <v>588</v>
+        <v>728</v>
       </c>
       <c r="E21" s="1">
-        <v>584</v>
+        <v>724</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2137,16 +2137,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>15.13018035888672</v>
+        <v>15.08718204498291</v>
       </c>
       <c r="C3" s="1">
-        <v>8467</v>
+        <v>8471</v>
       </c>
       <c r="D3" s="1">
         <v>1356</v>
       </c>
       <c r="E3" s="1">
-        <v>8262</v>
+        <v>8266</v>
       </c>
       <c r="F3" s="1">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>11.781418800354</v>
+        <v>11.7423906326294</v>
       </c>
       <c r="C4" s="1">
         <v>6593</v>
@@ -2189,7 +2189,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>9.737138748168945</v>
+        <v>9.70488166809082</v>
       </c>
       <c r="C5" s="1">
         <v>5449</v>
@@ -2215,7 +2215,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>6.731473922729492</v>
+        <v>6.709174156188965</v>
       </c>
       <c r="C6" s="1">
         <v>3767</v>
@@ -2241,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>6.177516460418701</v>
+        <v>6.157052040100098</v>
       </c>
       <c r="C7" s="1">
         <v>3457</v>
@@ -2267,16 +2267,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.924858570098877</v>
+        <v>4.983347415924072</v>
       </c>
       <c r="C8" s="1">
-        <v>2756</v>
+        <v>2798</v>
       </c>
       <c r="D8" s="1">
         <v>3162</v>
       </c>
       <c r="E8" s="1">
-        <v>2754</v>
+        <v>2796</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.399492740631104</v>
+        <v>4.384918212890625</v>
       </c>
       <c r="C9" s="1">
         <v>2462</v>
@@ -2319,7 +2319,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>4.202927112579346</v>
+        <v>4.189003944396973</v>
       </c>
       <c r="C10" s="1">
         <v>2352</v>
@@ -2345,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.41309118270874</v>
+        <v>3.401784658432007</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2371,7 +2371,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>3.082503795623779</v>
+        <v>3.072292327880859</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2397,7 +2397,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="2">
-        <v>2.383802890777588</v>
+        <v>2.375905990600586</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2423,7 +2423,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>1.972802519798279</v>
+        <v>1.966267108917236</v>
       </c>
       <c r="C14" s="1">
         <v>1104</v>
@@ -2449,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.522488832473755</v>
+        <v>1.51744532585144</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.51534104347229</v>
+        <v>1.510321140289307</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2501,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>1.322349548339844</v>
+        <v>1.317968845367432</v>
       </c>
       <c r="C17" s="1">
         <v>740</v>
@@ -2527,7 +2527,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1.315201640129089</v>
+        <v>1.310844779014587</v>
       </c>
       <c r="C18" s="1">
         <v>736</v>
@@ -2553,7 +2553,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="2">
-        <v>1.311627745628357</v>
+        <v>1.307282686233521</v>
       </c>
       <c r="C19" s="1">
         <v>734</v>
@@ -2576,25 +2576,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.143653631210327</v>
+        <v>1.29659640789032</v>
       </c>
       <c r="C20" s="1">
-        <v>640</v>
+        <v>728</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="1">
-        <v>640</v>
+        <v>724</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -2602,19 +2602,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>1.082897067070007</v>
+        <v>1.139865040779114</v>
       </c>
       <c r="C21" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>606</v>
+        <v>640</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2628,25 +2628,25 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
-        <v>1.050731778144836</v>
+        <v>1.079309701919556</v>
       </c>
       <c r="C22" s="1">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="D22" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2657,7 +2657,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9613838195800781</v>
+        <v>0.9581990242004395</v>
       </c>
       <c r="C23" s="1">
         <v>538</v>
@@ -2683,7 +2683,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="2">
-        <v>0.9578099250793457</v>
+        <v>0.9546369314193726</v>
       </c>
       <c r="C24" s="1">
         <v>536</v>
@@ -2709,7 +2709,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9470881223678589</v>
+        <v>0.9439507126808167</v>
       </c>
       <c r="C25" s="1">
         <v>530</v>
@@ -2735,7 +2735,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8291488885879517</v>
+        <v>0.8264021277427673</v>
       </c>
       <c r="C26" s="1">
         <v>464</v>
@@ -2761,7 +2761,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="2">
-        <v>0.7826879620552063</v>
+        <v>0.780095100402832</v>
       </c>
       <c r="C27" s="1">
         <v>438</v>
@@ -2787,7 +2787,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7290791869163513</v>
+        <v>0.7266639471054077</v>
       </c>
       <c r="C28" s="1">
         <v>408</v>
@@ -2813,7 +2813,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6576008200645447</v>
+        <v>0.6554223895072937</v>
       </c>
       <c r="C29" s="1">
         <v>368</v>
@@ -2839,7 +2839,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5968442559242249</v>
+        <v>0.5948670506477356</v>
       </c>
       <c r="C30" s="1">
         <v>334</v>
@@ -2865,7 +2865,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5325137376785278</v>
+        <v>0.5307496190071106</v>
       </c>
       <c r="C31" s="1">
         <v>298</v>
@@ -2891,7 +2891,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5074962973594666</v>
+        <v>0.5058150887489319</v>
       </c>
       <c r="C32" s="1">
         <v>284</v>
@@ -2917,7 +2917,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.5039224028587341</v>
+        <v>0.502252995967865</v>
       </c>
       <c r="C33" s="1">
         <v>282</v>
@@ -2943,7 +2943,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.5039224028587341</v>
+        <v>0.502252995967865</v>
       </c>
       <c r="C34" s="1">
         <v>282</v>
@@ -2969,7 +2969,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4789049625396729</v>
+        <v>0.4773184657096863</v>
       </c>
       <c r="C35" s="1">
         <v>268</v>
@@ -2995,7 +2995,7 @@
         <v>13</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4360179305076599</v>
+        <v>0.4345735311508179</v>
       </c>
       <c r="C36" s="1">
         <v>244</v>
@@ -3021,7 +3021,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.4324440360069275</v>
+        <v>0.431011438369751</v>
       </c>
       <c r="C37" s="1">
         <v>242</v>
@@ -3047,7 +3047,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4074265956878662</v>
+        <v>0.4060769081115723</v>
       </c>
       <c r="C38" s="1">
         <v>228</v>
@@ -3073,7 +3073,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.400278776884079</v>
+        <v>0.3989527523517609</v>
       </c>
       <c r="C39" s="1">
         <v>224</v>
@@ -3099,7 +3099,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.3967048525810242</v>
+        <v>0.395390659570694</v>
       </c>
       <c r="C40" s="1">
         <v>222</v>
@@ -3125,7 +3125,7 @@
         <v>44</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3788352608680725</v>
+        <v>0.3775802850723267</v>
       </c>
       <c r="C41" s="1">
         <v>212</v>
@@ -3151,7 +3151,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3716874122619629</v>
+        <v>0.3704561293125153</v>
       </c>
       <c r="C42" s="1">
         <v>208</v>
@@ -3177,7 +3177,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3323743343353272</v>
+        <v>0.3312732577323914</v>
       </c>
       <c r="C43" s="1">
         <v>186</v>
@@ -3203,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="2">
-        <v>0.3288004100322723</v>
+        <v>0.3277111947536469</v>
       </c>
       <c r="C44" s="1">
         <v>184</v>
@@ -3229,7 +3229,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3288004100322723</v>
+        <v>0.3277111947536469</v>
       </c>
       <c r="C45" s="1">
         <v>184</v>
@@ -3255,7 +3255,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.282339483499527</v>
+        <v>0.2814041674137116</v>
       </c>
       <c r="C46" s="1">
         <v>158</v>
@@ -3281,7 +3281,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.2787655591964722</v>
+        <v>0.277842104434967</v>
       </c>
       <c r="C47" s="1">
         <v>156</v>
@@ -3307,7 +3307,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2537481486797333</v>
+        <v>0.2529075443744659</v>
       </c>
       <c r="C48" s="1">
         <v>142</v>
@@ -3333,7 +3333,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2519612014293671</v>
+        <v>0.2511264979839325</v>
       </c>
       <c r="C49" s="1">
         <v>141</v>
@@ -3359,7 +3359,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2001393884420395</v>
+        <v>0.1994763761758804</v>
       </c>
       <c r="C50" s="1">
         <v>112</v>
@@ -3385,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1822697967290878</v>
+        <v>0.1816659867763519</v>
       </c>
       <c r="C51" s="1">
         <v>102</v>
@@ -3411,7 +3411,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1751219630241394</v>
+        <v>0.1745418310165405</v>
       </c>
       <c r="C52" s="1">
         <v>98</v>
@@ -3437,7 +3437,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1751219630241394</v>
+        <v>0.1745418310165405</v>
       </c>
       <c r="C53" s="1">
         <v>98</v>
@@ -3463,7 +3463,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.0857740193605423</v>
+        <v>0.08548987656831741</v>
       </c>
       <c r="C54" s="1">
         <v>48</v>
@@ -3489,7 +3489,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.0857740193605423</v>
+        <v>0.08548987656831741</v>
       </c>
       <c r="C55" s="1">
         <v>48</v>
@@ -3515,7 +3515,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.07862618565559387</v>
+        <v>0.07836572080850601</v>
       </c>
       <c r="C56" s="1">
         <v>44</v>
@@ -3541,7 +3541,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06790443509817123</v>
+        <v>0.06767948716878891</v>
       </c>
       <c r="C57" s="1">
         <v>38</v>
@@ -3567,7 +3567,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3593,7 +3593,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3619,7 +3619,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3645,7 +3645,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C61" s="1">
         <v>36</v>
@@ -3671,7 +3671,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C62" s="1">
         <v>36</v>
@@ -3697,7 +3697,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.06433051824569702</v>
+        <v>0.06411740928888321</v>
       </c>
       <c r="C63" s="1">
         <v>36</v>
@@ -3723,7 +3723,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.0571826808154583</v>
+        <v>0.05699324980378151</v>
       </c>
       <c r="C64" s="1">
         <v>32</v>
@@ -3749,7 +3749,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.0571826808154583</v>
+        <v>0.05699324980378151</v>
       </c>
       <c r="C65" s="1">
         <v>32</v>
@@ -3775,7 +3775,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.05360876396298409</v>
+        <v>0.05343117192387581</v>
       </c>
       <c r="C66" s="1">
         <v>30</v>
@@ -3801,7 +3801,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.05360876396298409</v>
+        <v>0.05343117192387581</v>
       </c>
       <c r="C67" s="1">
         <v>30</v>
@@ -3827,7 +3827,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.05003484711050987</v>
+        <v>0.04986909404397011</v>
       </c>
       <c r="C68" s="1">
         <v>28</v>
@@ -3853,7 +3853,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.04646092653274536</v>
+        <v>0.04630701616406441</v>
       </c>
       <c r="C69" s="1">
         <v>26</v>
@@ -3879,7 +3879,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.04646092653274536</v>
+        <v>0.04630701616406441</v>
       </c>
       <c r="C70" s="1">
         <v>26</v>
@@ -3905,7 +3905,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.03573917597532272</v>
+        <v>0.03562078252434731</v>
       </c>
       <c r="C71" s="1">
         <v>20</v>
@@ -3931,7 +3931,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02501742355525494</v>
+        <v>0.02493454702198505</v>
       </c>
       <c r="C72" s="1">
         <v>14</v>
@@ -3957,7 +3957,7 @@
         <v>17</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02144350484013557</v>
+        <v>0.02137246914207935</v>
       </c>
       <c r="C73" s="1">
         <v>12</v>
@@ -3983,7 +3983,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01429567020386457</v>
+        <v>0.01424831245094538</v>
       </c>
       <c r="C74" s="1">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01429567020386457</v>
+        <v>0.01424831245094538</v>
       </c>
       <c r="C75" s="1">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.007147835101932287</v>
+        <v>0.007124156225472689</v>
       </c>
       <c r="C76" s="1">
         <v>4</v>
@@ -4061,7 +4061,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.007147835101932287</v>
+        <v>0.007124156225472689</v>
       </c>
       <c r="C77" s="1">
         <v>4</v>
@@ -4087,7 +4087,7 @@
         <v>21</v>
       </c>
       <c r="B78" s="2">
-        <v>0.003573917550966144</v>
+        <v>0.003562078112736344</v>
       </c>
       <c r="C78" s="1">
         <v>2</v>

--- a/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
+++ b/Project/APP/MDK/McuSTUDIO_F470VET6_analysis.xlsx
@@ -647,31 +647,31 @@
                   <c:v>gd32f4xx_adc.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>btn_app.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>startup_gd32f450_470.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>gd32f4xx_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>gd32f4xx_fmc.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>ring_buffer.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>gd32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>gd32f4xx_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>btn_app.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>gd32f4xx_pmu.o</c:v>
@@ -818,232 +818,232 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="77"/>
                 <c:pt idx="0">
-                  <c:v>15.08718204498291</c:v>
+                  <c:v>15.08312511444092</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.7423906326294</c:v>
+                  <c:v>11.69780540466309</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.70488166809082</c:v>
+                  <c:v>9.668032646179199</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.709174156188965</c:v>
+                  <c:v>6.683699607849121</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.157052040100098</c:v>
+                  <c:v>6.133674144744873</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.983347415924072</c:v>
+                  <c:v>4.964425563812256</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.384918212890625</c:v>
+                  <c:v>4.368268966674805</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.189003944396973</c:v>
+                  <c:v>4.173098564147949</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.401784658432007</c:v>
+                  <c:v>3.388868093490601</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.072292327880859</c:v>
+                  <c:v>3.060626983642578</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.375905990600586</c:v>
+                  <c:v>2.36688494682312</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.966267108917236</c:v>
+                  <c:v>1.95880126953125</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.51744532585144</c:v>
+                  <c:v>1.511683583259583</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.510321140289307</c:v>
+                  <c:v>1.504586458206177</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.317968845367432</c:v>
+                  <c:v>1.312964677810669</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.310844779014587</c:v>
+                  <c:v>1.305867552757263</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.307282686233521</c:v>
+                  <c:v>1.302318930625916</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.29659640789032</c:v>
+                  <c:v>1.291673302650452</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.139865040779114</c:v>
+                  <c:v>1.135537028312683</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.079309701919556</c:v>
+                  <c:v>1.075211524963379</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.9581990242004395</c:v>
+                  <c:v>0.9545607566833496</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9546369314193726</c:v>
+                  <c:v>0.9510122537612915</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.9439507126808167</c:v>
+                  <c:v>0.9403665661811829</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8264021277427673</c:v>
+                  <c:v>0.8268128633499146</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.780095100402832</c:v>
+                  <c:v>0.8232643008232117</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.7266639471054077</c:v>
+                  <c:v>0.7771331071853638</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.6554223895072937</c:v>
+                  <c:v>0.7239048480987549</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.5948670506477356</c:v>
+                  <c:v>0.6529337763786316</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.5307496190071106</c:v>
+                  <c:v>0.5926083922386169</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.5058150887489319</c:v>
+                  <c:v>0.5287343859672546</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.502252995967865</c:v>
+                  <c:v>0.5038945078849793</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.502252995967865</c:v>
+                  <c:v>0.5003460049629211</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.4773184657096863</c:v>
+                  <c:v>0.4755061268806458</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.4345735311508179</c:v>
+                  <c:v>0.4329234659671783</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.431011438369751</c:v>
+                  <c:v>0.4293749332427979</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.4060769081115723</c:v>
+                  <c:v>0.4045350551605225</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.3989527523517609</c:v>
+                  <c:v>0.3974379301071167</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.395390659570694</c:v>
+                  <c:v>0.3938893973827362</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.3775802850723267</c:v>
+                  <c:v>0.3761466145515442</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3704561293125153</c:v>
+                  <c:v>0.3690495193004608</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.3312732577323914</c:v>
+                  <c:v>0.3300154507160187</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.3277111947536469</c:v>
+                  <c:v>0.3264668881893158</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.3277111947536469</c:v>
+                  <c:v>0.3264668881893158</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.2814041674137116</c:v>
+                  <c:v>0.2803356945514679</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.277842104434967</c:v>
+                  <c:v>0.276787132024765</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2529075443744659</c:v>
+                  <c:v>0.2519472539424896</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2511264979839325</c:v>
+                  <c:v>0.2501730024814606</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.1994763761758804</c:v>
+                  <c:v>0.1987189650535584</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.1816659867763519</c:v>
+                  <c:v>0.1809762120246887</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.1745418310165405</c:v>
+                  <c:v>0.1738791018724442</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.1745418310165405</c:v>
+                  <c:v>0.1738791018724442</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.08548987656831741</c:v>
+                  <c:v>0.08516527712345123</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.08548987656831741</c:v>
+                  <c:v>0.08516527712345123</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.07836572080850601</c:v>
+                  <c:v>0.07806816697120667</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.06767948716878891</c:v>
+                  <c:v>0.06742250919342041</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.06411740928888321</c:v>
+                  <c:v>0.06387395411729813</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.05699324980378151</c:v>
+                  <c:v>0.05677684769034386</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.05699324980378151</c:v>
+                  <c:v>0.05677684769034386</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.05343117192387581</c:v>
+                  <c:v>0.05322829633951187</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.05343117192387581</c:v>
+                  <c:v>0.05322829633951187</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.04986909404397011</c:v>
+                  <c:v>0.04967974126338959</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.04630701616406441</c:v>
+                  <c:v>0.0461311899125576</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.04630701616406441</c:v>
+                  <c:v>0.0461311899125576</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.03562078252434731</c:v>
+                  <c:v>0.03548553213477135</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.02493454702198505</c:v>
+                  <c:v>0.02483987063169479</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.02137246914207935</c:v>
+                  <c:v>0.02129131928086281</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01424831245094538</c:v>
+                  <c:v>0.01419421192258596</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01424831245094538</c:v>
+                  <c:v>0.01419421192258596</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.007124156225472689</c:v>
+                  <c:v>0.007097105961292982</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.007124156225472689</c:v>
+                  <c:v>0.007097105961292982</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.003562078112736344</c:v>
+                  <c:v>0.003548552980646491</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
@@ -1594,10 +1594,10 @@
         <v>1356</v>
       </c>
       <c r="D6" s="1">
-        <v>8471</v>
+        <v>8501</v>
       </c>
       <c r="E6" s="1">
-        <v>8266</v>
+        <v>8296</v>
       </c>
       <c r="F6" s="1">
         <v>200</v>
@@ -1646,10 +1646,10 @@
         <v>196</v>
       </c>
       <c r="D8" s="1">
-        <v>282</v>
+        <v>466</v>
       </c>
       <c r="E8" s="1">
-        <v>268</v>
+        <v>452</v>
       </c>
       <c r="F8" s="1">
         <v>14</v>
@@ -2137,16 +2137,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>15.08718204498291</v>
+        <v>15.08312511444092</v>
       </c>
       <c r="C3" s="1">
-        <v>8471</v>
+        <v>8501</v>
       </c>
       <c r="D3" s="1">
         <v>1356</v>
       </c>
       <c r="E3" s="1">
-        <v>8266</v>
+        <v>8296</v>
       </c>
       <c r="F3" s="1">
         <v>200</v>
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>11.7423906326294</v>
+        <v>11.69780540466309</v>
       </c>
       <c r="C4" s="1">
         <v>6593</v>
@@ -2189,7 +2189,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="2">
-        <v>9.70488166809082</v>
+        <v>9.668032646179199</v>
       </c>
       <c r="C5" s="1">
         <v>5449</v>
@@ -2215,7 +2215,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>6.709174156188965</v>
+        <v>6.683699607849121</v>
       </c>
       <c r="C6" s="1">
         <v>3767</v>
@@ -2241,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2">
-        <v>6.157052040100098</v>
+        <v>6.133674144744873</v>
       </c>
       <c r="C7" s="1">
         <v>3457</v>
@@ -2267,7 +2267,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>4.983347415924072</v>
+        <v>4.964425563812256</v>
       </c>
       <c r="C8" s="1">
         <v>2798</v>
@@ -2293,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.384918212890625</v>
+        <v>4.368268966674805</v>
       </c>
       <c r="C9" s="1">
         <v>2462</v>
@@ -2319,7 +2319,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="2">
-        <v>4.189003944396973</v>
+        <v>4.173098564147949</v>
       </c>
       <c r="C10" s="1">
         <v>2352</v>
@@ -2345,7 +2345,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.401784658432007</v>
+        <v>3.388868093490601</v>
       </c>
       <c r="C11" s="1">
         <v>1910</v>
@@ -2371,7 +2371,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2">
-        <v>3.072292327880859</v>
+        <v>3.060626983642578</v>
       </c>
       <c r="C12" s="1">
         <v>1725</v>
@@ -2397,7 +2397,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="2">
-        <v>2.375905990600586</v>
+        <v>2.36688494682312</v>
       </c>
       <c r="C13" s="1">
         <v>1334</v>
@@ -2423,7 +2423,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2">
-        <v>1.966267108917236</v>
+        <v>1.95880126953125</v>
       </c>
       <c r="C14" s="1">
         <v>1104</v>
@@ -2449,7 +2449,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="2">
-        <v>1.51744532585144</v>
+        <v>1.511683583259583</v>
       </c>
       <c r="C15" s="1">
         <v>852</v>
@@ -2475,7 +2475,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>1.510321140289307</v>
+        <v>1.504586458206177</v>
       </c>
       <c r="C16" s="1">
         <v>848</v>
@@ -2501,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="2">
-        <v>1.317968845367432</v>
+        <v>1.312964677810669</v>
       </c>
       <c r="C17" s="1">
         <v>740</v>
@@ -2527,7 +2527,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="2">
-        <v>1.310844779014587</v>
+        <v>1.305867552757263</v>
       </c>
       <c r="C18" s="1">
         <v>736</v>
@@ -2553,7 +2553,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="2">
-        <v>1.307282686233521</v>
+        <v>1.302318930625916</v>
       </c>
       <c r="C19" s="1">
         <v>734</v>
@@ -2579,7 +2579,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.29659640789032</v>
+        <v>1.291673302650452</v>
       </c>
       <c r="C20" s="1">
         <v>728</v>
@@ -2605,7 +2605,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="2">
-        <v>1.139865040779114</v>
+        <v>1.135537028312683</v>
       </c>
       <c r="C21" s="1">
         <v>640</v>
@@ -2631,7 +2631,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2">
-        <v>1.079309701919556</v>
+        <v>1.075211524963379</v>
       </c>
       <c r="C22" s="1">
         <v>606</v>
@@ -2657,7 +2657,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="2">
-        <v>0.9581990242004395</v>
+        <v>0.9545607566833496</v>
       </c>
       <c r="C23" s="1">
         <v>538</v>
@@ -2683,7 +2683,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="2">
-        <v>0.9546369314193726</v>
+        <v>0.9510122537612915</v>
       </c>
       <c r="C24" s="1">
         <v>536</v>
@@ -2709,7 +2709,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2">
-        <v>0.9439507126808167</v>
+        <v>0.9403665661811829</v>
       </c>
       <c r="C25" s="1">
         <v>530</v>
@@ -2732,71 +2732,71 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2">
-        <v>0.8264021277427673</v>
+        <v>0.8268128633499146</v>
       </c>
       <c r="C26" s="1">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D26" s="1">
-        <v>8192</v>
+        <v>196</v>
       </c>
       <c r="E26" s="1">
-        <v>36</v>
+        <v>452</v>
       </c>
       <c r="F26" s="1">
-        <v>428</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>8192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2">
-        <v>0.780095100402832</v>
+        <v>0.8232643008232117</v>
       </c>
       <c r="C27" s="1">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
       <c r="E27" s="1">
-        <v>438</v>
+        <v>36</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>8192</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2">
-        <v>0.7266639471054077</v>
+        <v>0.7771331071853638</v>
       </c>
       <c r="C28" s="1">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2810,19 +2810,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2">
-        <v>0.6554223895072937</v>
+        <v>0.7239048480987549</v>
       </c>
       <c r="C29" s="1">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2836,19 +2836,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2">
-        <v>0.5948670506477356</v>
+        <v>0.6529337763786316</v>
       </c>
       <c r="C30" s="1">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2862,19 +2862,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>0.5307496190071106</v>
+        <v>0.5926083922386169</v>
       </c>
       <c r="C31" s="1">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2888,19 +2888,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2">
-        <v>0.5058150887489319</v>
+        <v>0.5287343859672546</v>
       </c>
       <c r="C32" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2914,19 +2914,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2">
-        <v>0.502252995967865</v>
+        <v>0.5038945078849793</v>
       </c>
       <c r="C33" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -2940,28 +2940,28 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>0.502252995967865</v>
+        <v>0.5003460049629211</v>
       </c>
       <c r="C34" s="1">
         <v>282</v>
       </c>
       <c r="D34" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F34" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -2969,7 +2969,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>0.4773184657096863</v>
+        <v>0.4755061268806458</v>
       </c>
       <c r="C35" s="1">
         <v>268</v>
@@ -2995,7 +2995,7 @@
         <v>13</v>
       </c>
       <c r="B36" s="2">
-        <v>0.4345735311508179</v>
+        <v>0.4329234659671783</v>
       </c>
       <c r="C36" s="1">
         <v>244</v>
@@ -3021,7 +3021,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>0.431011438369751</v>
+        <v>0.4293749332427979</v>
       </c>
       <c r="C37" s="1">
         <v>242</v>
@@ -3047,7 +3047,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>0.4060769081115723</v>
+        <v>0.4045350551605225</v>
       </c>
       <c r="C38" s="1">
         <v>228</v>
@@ -3073,7 +3073,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>0.3989527523517609</v>
+        <v>0.3974379301071167</v>
       </c>
       <c r="C39" s="1">
         <v>224</v>
@@ -3099,7 +3099,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.395390659570694</v>
+        <v>0.3938893973827362</v>
       </c>
       <c r="C40" s="1">
         <v>222</v>
@@ -3125,7 +3125,7 @@
         <v>44</v>
       </c>
       <c r="B41" s="2">
-        <v>0.3775802850723267</v>
+        <v>0.3761466145515442</v>
       </c>
       <c r="C41" s="1">
         <v>212</v>
@@ -3151,7 +3151,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2">
-        <v>0.3704561293125153</v>
+        <v>0.3690495193004608</v>
       </c>
       <c r="C42" s="1">
         <v>208</v>
@@ -3177,7 +3177,7 @@
         <v>45</v>
       </c>
       <c r="B43" s="2">
-        <v>0.3312732577323914</v>
+        <v>0.3300154507160187</v>
       </c>
       <c r="C43" s="1">
         <v>186</v>
@@ -3203,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="B44" s="2">
-        <v>0.3277111947536469</v>
+        <v>0.3264668881893158</v>
       </c>
       <c r="C44" s="1">
         <v>184</v>
@@ -3229,7 +3229,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.3277111947536469</v>
+        <v>0.3264668881893158</v>
       </c>
       <c r="C45" s="1">
         <v>184</v>
@@ -3255,7 +3255,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.2814041674137116</v>
+        <v>0.2803356945514679</v>
       </c>
       <c r="C46" s="1">
         <v>158</v>
@@ -3281,7 +3281,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.277842104434967</v>
+        <v>0.276787132024765</v>
       </c>
       <c r="C47" s="1">
         <v>156</v>
@@ -3307,7 +3307,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2529075443744659</v>
+        <v>0.2519472539424896</v>
       </c>
       <c r="C48" s="1">
         <v>142</v>
@@ -3333,7 +3333,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2511264979839325</v>
+        <v>0.2501730024814606</v>
       </c>
       <c r="C49" s="1">
         <v>141</v>
@@ -3359,7 +3359,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2">
-        <v>0.1994763761758804</v>
+        <v>0.1987189650535584</v>
       </c>
       <c r="C50" s="1">
         <v>112</v>
@@ -3385,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2">
-        <v>0.1816659867763519</v>
+        <v>0.1809762120246887</v>
       </c>
       <c r="C51" s="1">
         <v>102</v>
@@ -3411,7 +3411,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>0.1745418310165405</v>
+        <v>0.1738791018724442</v>
       </c>
       <c r="C52" s="1">
         <v>98</v>
@@ -3437,7 +3437,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>0.1745418310165405</v>
+        <v>0.1738791018724442</v>
       </c>
       <c r="C53" s="1">
         <v>98</v>
@@ -3463,7 +3463,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>0.08548987656831741</v>
+        <v>0.08516527712345123</v>
       </c>
       <c r="C54" s="1">
         <v>48</v>
@@ -3489,7 +3489,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2">
-        <v>0.08548987656831741</v>
+        <v>0.08516527712345123</v>
       </c>
       <c r="C55" s="1">
         <v>48</v>
@@ -3515,7 +3515,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2">
-        <v>0.07836572080850601</v>
+        <v>0.07806816697120667</v>
       </c>
       <c r="C56" s="1">
         <v>44</v>
@@ -3541,7 +3541,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2">
-        <v>0.06767948716878891</v>
+        <v>0.06742250919342041</v>
       </c>
       <c r="C57" s="1">
         <v>38</v>
@@ -3567,7 +3567,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C58" s="1">
         <v>36</v>
@@ -3593,7 +3593,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C59" s="1">
         <v>36</v>
@@ -3619,7 +3619,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C60" s="1">
         <v>36</v>
@@ -3645,7 +3645,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C61" s="1">
         <v>36</v>
@@ -3671,7 +3671,7 @@
         <v>62</v>
       </c>
       <c r="B62" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C62" s="1">
         <v>36</v>
@@ -3697,7 +3697,7 @@
         <v>63</v>
       </c>
       <c r="B63" s="2">
-        <v>0.06411740928888321</v>
+        <v>0.06387395411729813</v>
       </c>
       <c r="C63" s="1">
         <v>36</v>
@@ -3723,7 +3723,7 @@
         <v>64</v>
       </c>
       <c r="B64" s="2">
-        <v>0.05699324980378151</v>
+        <v>0.05677684769034386</v>
       </c>
       <c r="C64" s="1">
         <v>32</v>
@@ -3749,7 +3749,7 @@
         <v>65</v>
       </c>
       <c r="B65" s="2">
-        <v>0.05699324980378151</v>
+        <v>0.05677684769034386</v>
       </c>
       <c r="C65" s="1">
         <v>32</v>
@@ -3775,7 +3775,7 @@
         <v>66</v>
       </c>
       <c r="B66" s="2">
-        <v>0.05343117192387581</v>
+        <v>0.05322829633951187</v>
       </c>
       <c r="C66" s="1">
         <v>30</v>
@@ -3801,7 +3801,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="2">
-        <v>0.05343117192387581</v>
+        <v>0.05322829633951187</v>
       </c>
       <c r="C67" s="1">
         <v>30</v>
@@ -3827,7 +3827,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="2">
-        <v>0.04986909404397011</v>
+        <v>0.04967974126338959</v>
       </c>
       <c r="C68" s="1">
         <v>28</v>
@@ -3853,7 +3853,7 @@
         <v>69</v>
       </c>
       <c r="B69" s="2">
-        <v>0.04630701616406441</v>
+        <v>0.0461311899125576</v>
       </c>
       <c r="C69" s="1">
         <v>26</v>
@@ -3879,7 +3879,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="2">
-        <v>0.04630701616406441</v>
+        <v>0.0461311899125576</v>
       </c>
       <c r="C70" s="1">
         <v>26</v>
@@ -3905,7 +3905,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="2">
-        <v>0.03562078252434731</v>
+        <v>0.03548553213477135</v>
       </c>
       <c r="C71" s="1">
         <v>20</v>
@@ -3931,7 +3931,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="2">
-        <v>0.02493454702198505</v>
+        <v>0.02483987063169479</v>
       </c>
       <c r="C72" s="1">
         <v>14</v>
@@ -3957,7 +3957,7 @@
         <v>17</v>
       </c>
       <c r="B73" s="2">
-        <v>0.02137246914207935</v>
+        <v>0.02129131928086281</v>
       </c>
       <c r="C73" s="1">
         <v>12</v>
@@ -3983,7 +3983,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01424831245094538</v>
+        <v>0.01419421192258596</v>
       </c>
       <c r="C74" s="1">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01424831245094538</v>
+        <v>0.01419421192258596</v>
       </c>
       <c r="C75" s="1">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2">
-        <v>0.007124156225472689</v>
+        <v>0.007097105961292982</v>
       </c>
       <c r="C76" s="1">
         <v>4</v>
@@ -4061,7 +4061,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2">
-        <v>0.007124156225472689</v>
+        <v>0.007097105961292982</v>
       </c>
       <c r="C77" s="1">
         <v>4</v>
@@ -4087,7 +4087,7 @@
         <v>21</v>
       </c>
       <c r="B78" s="2">
-        <v>0.003562078112736344</v>
+        <v>0.003548552980646491</v>
       </c>
       <c r="C78" s="1">
         <v>2</v>
